--- a/output/yearly_surface_area_iteration_65_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_65_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.8449763746108</v>
+        <v>10.84497643830257</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907208963649</v>
+        <v>37.789072311569</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.172828653676444</v>
+        <v>7.39648720379547</v>
       </c>
       <c r="C2" t="n">
-        <v>3.926990816987241</v>
+        <v>5.928774385946488</v>
       </c>
       <c r="D2" t="n">
-        <v>16.13600526700058</v>
+        <v>29.85592943384975</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.3131207643925</v>
+        <v>18.8691908756237</v>
       </c>
       <c r="C3" t="n">
-        <v>22.91890015564179</v>
+        <v>27.30731239362503</v>
       </c>
       <c r="D3" t="n">
-        <v>54.13847715069036</v>
+        <v>72.41371066524474</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.49236398810894</v>
+        <v>38.44131310748811</v>
       </c>
       <c r="C4" t="n">
-        <v>60.25280185273949</v>
+        <v>71.0373003838907</v>
       </c>
       <c r="D4" t="n">
-        <v>63.41795645123121</v>
+        <v>107.2961883448382</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.03200643027521</v>
+        <v>44.93950116189775</v>
       </c>
       <c r="C5" t="n">
-        <v>82.3686323863074</v>
+        <v>98.61655689159213</v>
       </c>
       <c r="D5" t="n">
-        <v>46.33849164044945</v>
+        <v>85.01935118777379</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.62021217383928</v>
+        <v>40.85543071223103</v>
       </c>
       <c r="C6" t="n">
-        <v>107.2706629045278</v>
+        <v>114.5159609618692</v>
       </c>
       <c r="D6" t="n">
-        <v>38.44033135978387</v>
+        <v>54.17872880656449</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>29.46421209985527</v>
+        <v>27.66761380108361</v>
       </c>
       <c r="C7" t="n">
-        <v>102.7055360797801</v>
+        <v>118.1562814492164</v>
       </c>
       <c r="D7" t="n">
-        <v>37.72856427420492</v>
+        <v>40.48334833232147</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>15.43798264928109</v>
+        <v>14.52004854581032</v>
       </c>
       <c r="C8" t="n">
-        <v>70.76437452211009</v>
+        <v>84.44993751931062</v>
       </c>
       <c r="D8" t="n">
-        <v>36.55046702910875</v>
+        <v>36.04977569994287</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.765624340592267</v>
+        <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>43.37655881673681</v>
+        <v>46.48280855297372</v>
       </c>
       <c r="D9" t="n">
-        <v>34.16874709860598</v>
+        <v>33.9468721174462</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.551783267515713</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
         <v>31.60245859970483</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>34.87658719336794</v>
       </c>
     </row>
     <row r="11">
@@ -906,10 +906,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>30.20837685967435</v>
+        <v>28.96450251839364</v>
       </c>
       <c r="D11" t="n">
         <v>35.53926689373453</v>
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>28.20561154301086</v>
+        <v>27.55471281509523</v>
       </c>
       <c r="D12" t="n">
-        <v>35.36549755008285</v>
+        <v>34.93156506480576</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.49598787928967</v>
+        <v>25.23582473766426</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>31.73990327829938</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>23.04652735719387</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -965,7 +965,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.85861263505523</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
         <v>29.38370878810703</v>
@@ -979,10 +979,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.42584182393164</v>
+        <v>19.01252604044373</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -993,7 +993,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
         <v>24.0832529328785</v>
@@ -1007,7 +1007,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -1021,10 +1021,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.721035897720284</v>
+        <v>7.660526008721306</v>
       </c>
       <c r="C21" t="n">
-        <v>96.51294872150355</v>
+        <v>92.88387785574584</v>
       </c>
       <c r="D21" t="n">
-        <v>8.686165384935318</v>
+        <v>7.660526008721306</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.39903153628071</v>
+        <v>7.199155915241861</v>
       </c>
       <c r="C2" t="n">
-        <v>12.54280866945725</v>
+        <v>7.666467822463342</v>
       </c>
       <c r="D2" t="n">
-        <v>16.0967353588307</v>
+        <v>33.49330467808419</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.36220814960484</v>
+        <v>21.61317570899353</v>
       </c>
       <c r="C3" t="n">
-        <v>18.72683745850791</v>
+        <v>24.98547907308132</v>
       </c>
       <c r="D3" t="n">
-        <v>54.2317431825938</v>
+        <v>77.99985510240909</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.8887690764464</v>
+        <v>37.11399021134642</v>
       </c>
       <c r="C4" t="n">
-        <v>58.08313942635404</v>
+        <v>69.53129940557609</v>
       </c>
       <c r="D4" t="n">
-        <v>74.85335371029807</v>
+        <v>117.2383473457456</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52.67076433284139</v>
+        <v>50.29002615004288</v>
       </c>
       <c r="C5" t="n">
-        <v>97.04576056479723</v>
+        <v>112.7537238327462</v>
       </c>
       <c r="D5" t="n">
-        <v>56.81864838328416</v>
+        <v>100.2364406035994</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>52.89067581859268</v>
+        <v>49.63029169278902</v>
       </c>
       <c r="C6" t="n">
-        <v>118.1788616464141</v>
+        <v>134.2392723401876</v>
       </c>
       <c r="D6" t="n">
-        <v>44.03531152628644</v>
+        <v>66.53598715991909</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>39.76470901281281</v>
+        <v>37.12969817461437</v>
       </c>
       <c r="C7" t="n">
-        <v>129.4149641215188</v>
+        <v>139.416027984681</v>
       </c>
       <c r="D7" t="n">
-        <v>40.00425545264903</v>
+        <v>45.51382356888213</v>
       </c>
     </row>
     <row r="8">
@@ -1175,10 +1175,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>23.36559536107409</v>
+        <v>21.61317570899353</v>
       </c>
       <c r="C8" t="n">
-        <v>102.641722479004</v>
+        <v>117.3286681345363</v>
       </c>
       <c r="D8" t="n">
         <v>38.63668090063322</v>
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>11.6484365108884</v>
+        <v>10.6499990956694</v>
       </c>
       <c r="C9" t="n">
-        <v>65.67499442329461</v>
+        <v>73.44061876388687</v>
       </c>
       <c r="D9" t="n">
-        <v>35.49999698556465</v>
+        <v>35.16718451382499</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.548257187326225</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>41.70955121492574</v>
+        <v>42.13661146627311</v>
       </c>
       <c r="D10" t="n">
-        <v>36.30012136452581</v>
+        <v>35.58835427894688</v>
       </c>
     </row>
     <row r="11">
@@ -1220,10 +1220,10 @@
         <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>32.87382187670443</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>35.7169632282032</v>
       </c>
     </row>
     <row r="12">
@@ -1231,10 +1231,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>31.46010518258904</v>
+        <v>29.94134148411922</v>
       </c>
       <c r="D12" t="n">
         <v>35.58246379272139</v>
@@ -1248,10 +1248,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>28.09761929554372</v>
+        <v>27.83745615391831</v>
       </c>
       <c r="D13" t="n">
-        <v>33.30088212805181</v>
+        <v>32.5203927031756</v>
       </c>
     </row>
     <row r="14">
@@ -1262,7 +1262,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>26.11939767148639</v>
+        <v>24.89024954576939</v>
       </c>
       <c r="D14" t="n">
         <v>30.72870314292517</v>
@@ -1276,7 +1276,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>23.65030219530566</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
         <v>29.74204670015712</v>
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.07910495788326</v>
+        <v>20.25247339090745</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>18.88882582970863</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1318,7 +1318,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.912310274595395</v>
+        <v>7.83593805310645</v>
       </c>
       <c r="C21" t="n">
-        <v>105.8271499227134</v>
+        <v>100.8877024337455</v>
       </c>
       <c r="D21" t="n">
-        <v>9.890387843244245</v>
+        <v>8.815430309744755</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>10.07273144557227</v>
+        <v>7.51331518060084</v>
       </c>
       <c r="C2" t="n">
-        <v>9.987319395302803</v>
+        <v>10.37707323388879</v>
       </c>
       <c r="D2" t="n">
-        <v>15.84540794654352</v>
+        <v>29.02831611916969</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.10971906316416</v>
+        <v>22.25131171675396</v>
       </c>
       <c r="C3" t="n">
-        <v>33.4285093296039</v>
+        <v>27.22877257728529</v>
       </c>
       <c r="D3" t="n">
-        <v>54.0304849032232</v>
+        <v>83.74307917225292</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.02541193378595</v>
+        <v>37.94356702143497</v>
       </c>
       <c r="C4" t="n">
-        <v>51.98255919216436</v>
+        <v>65.48551711637499</v>
       </c>
       <c r="D4" t="n">
-        <v>82.01323971737004</v>
+        <v>124.8576912784051</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>53.08800710714628</v>
+        <v>52.0817157102933</v>
       </c>
       <c r="C5" t="n">
-        <v>101.6354310821511</v>
+        <v>117.9569866652543</v>
       </c>
       <c r="D5" t="n">
-        <v>68.45235867860886</v>
+        <v>115.2080930933632</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>61.58503348740243</v>
+        <v>56.91584140600459</v>
       </c>
       <c r="C6" t="n">
-        <v>133.5952458462017</v>
+        <v>153.4795638480166</v>
       </c>
       <c r="D6" t="n">
-        <v>50.07305990740432</v>
+        <v>78.16871570753956</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>50.00531931581128</v>
+        <v>46.47200932822701</v>
       </c>
       <c r="C7" t="n">
-        <v>149.3572052378842</v>
+        <v>161.5740736695315</v>
       </c>
       <c r="D7" t="n">
-        <v>43.29801900039708</v>
+        <v>52.34089710421445</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>32.12769362147687</v>
+        <v>29.04009709162065</v>
       </c>
       <c r="C8" t="n">
-        <v>133.5176877775662</v>
+        <v>145.5342796775471</v>
       </c>
       <c r="D8" t="n">
-        <v>40.13875488813084</v>
+        <v>40.97324043674063</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16.86249856814321</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>93.40936706826699</v>
+        <v>104.0593661639364</v>
       </c>
       <c r="D9" t="n">
-        <v>37.27499683484289</v>
+        <v>36.83124687252333</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.683558444063038</v>
+        <v>7.829437941368314</v>
       </c>
       <c r="C10" t="n">
-        <v>58.36490101747288</v>
+        <v>60.07314202286233</v>
       </c>
       <c r="D10" t="n">
-        <v>36.72718161587318</v>
+        <v>35.87306111317846</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.508586368528851</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>39.98167525545134</v>
+        <v>39.27088991757665</v>
       </c>
       <c r="D11" t="n">
-        <v>36.96083756948391</v>
+        <v>36.25005223160922</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.339324852770901</v>
+        <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>34.71459882216721</v>
+        <v>33.1958351236974</v>
       </c>
       <c r="D12" t="n">
-        <v>35.79943003535993</v>
+        <v>35.58246379272139</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>30.95941385342317</v>
+        <v>29.91876128692155</v>
       </c>
       <c r="D13" t="n">
-        <v>33.82120841130262</v>
+        <v>33.04071898642641</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>28.27040689149115</v>
+        <v>27.04125876577415</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -1587,7 +1587,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>25.44199175555609</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
         <v>29.74204670015712</v>
@@ -1601,10 +1601,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>22.7323680918349</v>
+        <v>21.49242074137117</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -1615,10 +1615,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>20.30548776693678</v>
+        <v>19.36104647545135</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1629,7 +1629,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>19.26188995732242</v>
+        <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.088942832815791</v>
+        <v>7.995649956573629</v>
       </c>
       <c r="C21" t="n">
-        <v>114.256317513523</v>
+        <v>108.9407306583157</v>
       </c>
       <c r="D21" t="n">
-        <v>11.12229639512171</v>
+        <v>9.994562445717037</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.817076131840604</v>
+        <v>7.004769869800992</v>
       </c>
       <c r="C2" t="n">
-        <v>6.551202430438965</v>
+        <v>7.139269305282806</v>
       </c>
       <c r="D2" t="n">
-        <v>12.96397843457913</v>
+        <v>24.02631156603219</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.6846633649543</v>
+        <v>26.45810062945154</v>
       </c>
       <c r="C3" t="n">
-        <v>46.95699269412494</v>
+        <v>42.34768722268617</v>
       </c>
       <c r="D3" t="n">
-        <v>59.81297888123692</v>
+        <v>91.12582190818894</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.49991487010665</v>
+        <v>25.01493150420873</v>
       </c>
       <c r="C4" t="n">
-        <v>80.67315410107314</v>
+        <v>94.71214627180254</v>
       </c>
       <c r="D4" t="n">
-        <v>78.58006799561895</v>
+        <v>122.9049950946582</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.68023765251858</v>
+        <v>32.05406254365837</v>
       </c>
       <c r="C5" t="n">
-        <v>79.81608835526569</v>
+        <v>91.6952355766521</v>
       </c>
       <c r="D5" t="n">
-        <v>48.96466674930968</v>
+        <v>77.65624340592271</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.03402667894593</v>
+        <v>28.86043726174349</v>
       </c>
       <c r="C6" t="n">
-        <v>98.3750469563474</v>
+        <v>106.4253781311713</v>
       </c>
       <c r="D6" t="n">
-        <v>28.49817235887642</v>
+        <v>34.45541742824607</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.25974653546468</v>
+        <v>19.22360179685679</v>
       </c>
       <c r="C7" t="n">
-        <v>93.90220441579891</v>
+        <v>102.3462164200257</v>
       </c>
       <c r="D7" t="n">
-        <v>28.20659329071511</v>
+        <v>28.80545939030566</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.68279768053704</v>
+        <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>68.84505776030758</v>
+        <v>76.68922191723958</v>
       </c>
       <c r="D8" t="n">
-        <v>27.45457454926205</v>
+        <v>27.12078032981814</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.212499472473814</v>
+        <v>5.546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>44.48593372253571</v>
+        <v>45.81718360949438</v>
       </c>
       <c r="D9" t="n">
-        <v>27.95624762613216</v>
+        <v>27.29062268265283</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.98589567924205</v>
+        <v>3.843542262126263</v>
       </c>
       <c r="C10" t="n">
-        <v>31.31775176547326</v>
+        <v>30.7483380970101</v>
       </c>
       <c r="D10" t="n">
-        <v>28.89774367450487</v>
+        <v>28.32833000604172</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.198534020436107</v>
+        <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>27.72062817711293</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>28.60910984945629</v>
+        <v>28.43141351498762</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>25.16808414607123</v>
+        <v>24.30021917551705</v>
       </c>
       <c r="D12" t="n">
-        <v>27.55471281509523</v>
+        <v>26.90381408717959</v>
       </c>
     </row>
     <row r="13">
@@ -1870,7 +1870,7 @@
         <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>23.41468274628643</v>
+        <v>22.37403017978481</v>
       </c>
       <c r="D13" t="n">
         <v>25.49598787928967</v>
@@ -1884,7 +1884,7 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>21.20280516861837</v>
+        <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
         <v>24.89024954576939</v>
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.99190933865455</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
-        <v>22.93362637120549</v>
+        <v>22.21695054710532</v>
       </c>
     </row>
     <row r="16">
@@ -1912,10 +1912,10 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>20.25247339090745</v>
       </c>
     </row>
     <row r="17">
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
         <v>17.9443845382232</v>
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>15.51652246562084</v>
       </c>
       <c r="D18" t="n">
-        <v>14.44641746799181</v>
+        <v>13.9113649691773</v>
       </c>
     </row>
     <row r="19">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
       <c r="D19" t="n">
         <v>9.027170140549421</v>
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>75.31968386981528</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>6.724971774090649</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.098215828153687</v>
+        <v>4.225442119078272</v>
       </c>
       <c r="C2" t="n">
-        <v>3.0012027318825</v>
+        <v>3.522510762837555</v>
       </c>
       <c r="D2" t="n">
-        <v>9.219592690581797</v>
+        <v>17.66654993792135</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>27.72455516792992</v>
+        <v>26.08503650183775</v>
       </c>
       <c r="C3" t="n">
-        <v>36.23630776374977</v>
+        <v>35.70125526493526</v>
       </c>
       <c r="D3" t="n">
-        <v>57.56477663851173</v>
+        <v>90.69385291832035</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.74012426247764</v>
+        <v>35.90153179660161</v>
       </c>
       <c r="C4" t="n">
-        <v>102.3697783649277</v>
+        <v>103.4673722982756</v>
       </c>
       <c r="D4" t="n">
-        <v>88.75195595932014</v>
+        <v>136.7653091832146</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.50905369908114</v>
+        <v>36.00559705325178</v>
       </c>
       <c r="C5" t="n">
-        <v>114.5208697003904</v>
+        <v>130.6460757426443</v>
       </c>
       <c r="D5" t="n">
-        <v>62.14462967882311</v>
+        <v>96.57943040527999</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.8768081775462</v>
+        <v>34.37491411649783</v>
       </c>
       <c r="C6" t="n">
-        <v>115.2002391117292</v>
+        <v>126.6317093799791</v>
       </c>
       <c r="D6" t="n">
-        <v>34.69692736349078</v>
+        <v>43.9548082145382</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.12190094624263</v>
+        <v>17.96598298771663</v>
       </c>
       <c r="C7" t="n">
-        <v>117.5574153496258</v>
+        <v>126.1212005737707</v>
       </c>
       <c r="D7" t="n">
-        <v>30.42239785920016</v>
+        <v>31.9794497181356</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.930378028456486</v>
+        <v>8.762098260402782</v>
       </c>
       <c r="C8" t="n">
-        <v>90.37478491444013</v>
+        <v>97.88515485192822</v>
       </c>
       <c r="D8" t="n">
-        <v>28.70630287217673</v>
+        <v>27.87181732356695</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.992187076095029</v>
+        <v>4.659374604355361</v>
       </c>
       <c r="C9" t="n">
-        <v>51.58593311964863</v>
+        <v>51.03124566674919</v>
       </c>
       <c r="D9" t="n">
-        <v>29.17656002251095</v>
+        <v>28.28906009787183</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.420008090968388</v>
+        <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>34.16482010778901</v>
+        <v>32.74128593663113</v>
       </c>
       <c r="D10" t="n">
-        <v>29.89421759431538</v>
+        <v>29.60951076008381</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>30.38607319414302</v>
+        <v>29.14219885286231</v>
       </c>
       <c r="D11" t="n">
-        <v>29.852984190737</v>
+        <v>29.31989518733098</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>21.91359050649305</v>
+        <v>20.61179305066178</v>
       </c>
       <c r="D12" t="n">
-        <v>28.63954402828795</v>
+        <v>28.20561154301086</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>17.43093048890212</v>
+        <v>16.65044106402591</v>
       </c>
       <c r="D13" t="n">
-        <v>26.27647730416588</v>
+        <v>26.01631416254048</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.67163860289184</v>
+        <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>18.4372218857551</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>14.69185439405351</v>
+        <v>13.97517856995334</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -2223,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.05273663858884</v>
+        <v>13.63942085510094</v>
       </c>
       <c r="D16" t="n">
         <v>15.29268398905256</v>
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>13.22217808079604</v>
       </c>
       <c r="D17" t="n">
-        <v>12.27773678931061</v>
+        <v>11.8055161435679</v>
       </c>
     </row>
     <row r="18">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>13.9113649691773</v>
       </c>
       <c r="D18" t="n">
         <v>7.490734983403163</v>
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>65.59743635465912</v>
+        <v>63.79200232654924</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>5.416302084329653</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.793293202760428</v>
+        <v>4.684900044665779</v>
       </c>
       <c r="C2" t="n">
-        <v>8.498008127960391</v>
+        <v>6.71024555852695</v>
       </c>
       <c r="D2" t="n">
-        <v>17.95616551067416</v>
+        <v>16.22239906497429</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.40348261091221</v>
+        <v>20.20927649192059</v>
       </c>
       <c r="C3" t="n">
-        <v>22.48202242725196</v>
+        <v>23.97918767622835</v>
       </c>
       <c r="D3" t="n">
-        <v>51.94917977021998</v>
+        <v>84.2732229325462</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.47807974090174</v>
+        <v>42.65301075870693</v>
       </c>
       <c r="C4" t="n">
-        <v>96.98391045942965</v>
+        <v>96.10328276872026</v>
       </c>
       <c r="D4" t="n">
-        <v>96.57550341446299</v>
+        <v>148.7622661291107</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.38128762880881</v>
+        <v>43.95775345765094</v>
       </c>
       <c r="C5" t="n">
-        <v>152.4408747769235</v>
+        <v>161.301147807751</v>
       </c>
       <c r="D5" t="n">
-        <v>77.95076771719675</v>
+        <v>119.1841712955628</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>45.24286120251001</v>
+        <v>40.69442408873454</v>
       </c>
       <c r="C6" t="n">
-        <v>149.2933916371082</v>
+        <v>164.1060009987841</v>
       </c>
       <c r="D6" t="n">
-        <v>44.51833139677587</v>
+        <v>59.81396062894117</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>30.48228446915921</v>
+        <v>27.06874770149305</v>
       </c>
       <c r="C7" t="n">
-        <v>141.7516057730842</v>
+        <v>154.1481340346087</v>
       </c>
       <c r="D7" t="n">
-        <v>33.17718191731671</v>
+        <v>36.23139902522853</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.77039421039326</v>
+        <v>12.60073178400781</v>
       </c>
       <c r="C8" t="n">
-        <v>123.7542068588317</v>
+        <v>130.0128484734051</v>
       </c>
       <c r="D8" t="n">
-        <v>30.20837685967435</v>
+        <v>29.70768553050848</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.767186925373262</v>
+        <v>5.990624491314035</v>
       </c>
       <c r="C9" t="n">
-        <v>78.87655580230145</v>
+        <v>80.87343063273947</v>
       </c>
       <c r="D9" t="n">
-        <v>30.28593492830985</v>
+        <v>29.28749751309084</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.989421759431538</v>
+        <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
-        <v>46.40721397974673</v>
+        <v>44.55661955724149</v>
       </c>
       <c r="D10" t="n">
-        <v>30.32127784566274</v>
+        <v>29.89421759431538</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>34.82848155585983</v>
+        <v>33.22921454564179</v>
       </c>
       <c r="D11" t="n">
-        <v>30.56376952861169</v>
+        <v>29.852984190737</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>26.68684784454105</v>
+        <v>25.16808414607123</v>
       </c>
       <c r="D12" t="n">
-        <v>29.50740899884213</v>
+        <v>28.63954402828795</v>
       </c>
     </row>
     <row r="13">
@@ -2492,7 +2492,7 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>20.03256190515617</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
         <v>26.53664044579129</v>
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.90078672860884</v>
+        <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>19.97365704290136</v>
+        <v>19.0517959486136</v>
       </c>
     </row>
     <row r="15">
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>15.40853021815369</v>
       </c>
       <c r="D15" t="n">
         <v>17.20021977840412</v>
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>15.29268398905256</v>
+        <v>14.46605242207675</v>
       </c>
       <c r="D16" t="n">
         <v>14.87936820556466</v>
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>14.16661937228147</v>
       </c>
       <c r="D17" t="n">
-        <v>11.33329549782518</v>
+        <v>10.86107485208246</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>34.24335992412875</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>34.3032465340878</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>3.610868056219768</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.350704914594364</v>
+        <v>2.77638250760998</v>
       </c>
       <c r="C2" t="n">
-        <v>3.78267390446296</v>
+        <v>3.145519644406781</v>
       </c>
       <c r="D2" t="n">
-        <v>12.41321797249667</v>
+        <v>11.37256540599505</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.21342446691583</v>
+        <v>20.41053477129119</v>
       </c>
       <c r="C3" t="n">
-        <v>28.89283493598363</v>
+        <v>26.46300936797277</v>
       </c>
       <c r="D3" t="n">
-        <v>54.93860152965151</v>
+        <v>82.05447312094842</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>49.74908316500287</v>
+        <v>46.37972504402781</v>
       </c>
       <c r="C4" t="n">
-        <v>91.5214662330004</v>
+        <v>92.29999216246813</v>
       </c>
       <c r="D4" t="n">
-        <v>101.961371319961</v>
+        <v>158.0407636819473</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.13018120069989</v>
+        <v>45.33220024359647</v>
       </c>
       <c r="C5" t="n">
-        <v>180.2734221923206</v>
+        <v>192.00530725807</v>
       </c>
       <c r="D5" t="n">
-        <v>84.6021084134689</v>
+        <v>125.4428129101362</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.15856976866503</v>
+        <v>33.32837106377072</v>
       </c>
       <c r="C6" t="n">
-        <v>189.1022792966122</v>
+        <v>197.3538687508066</v>
       </c>
       <c r="D6" t="n">
-        <v>44.47807974090175</v>
+        <v>58.12339108222817</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.761517423326035</v>
+        <v>8.324238784308704</v>
       </c>
       <c r="C7" t="n">
-        <v>155.525526063667</v>
+        <v>164.2689711176891</v>
       </c>
       <c r="D7" t="n">
-        <v>33.83593462686632</v>
+        <v>35.81219275551515</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.673119072214817</v>
+        <v>4.088979188187965</v>
       </c>
       <c r="C8" t="n">
-        <v>98.13550051651117</v>
+        <v>99.05343461998193</v>
       </c>
       <c r="D8" t="n">
-        <v>32.21114217633784</v>
+        <v>31.37665662772806</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.107812321017901</v>
+        <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>35.38905949498476</v>
+        <v>33.9468721174462</v>
       </c>
       <c r="D9" t="n">
-        <v>32.28280975874785</v>
+        <v>31.39530983410874</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>26.05067533218912</v>
       </c>
       <c r="D10" t="n">
-        <v>23.91537407545231</v>
+        <v>23.34596040698915</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>21.32356013624072</v>
+        <v>20.07968579496001</v>
       </c>
       <c r="D11" t="n">
-        <v>23.63361248433346</v>
+        <v>22.92282714645877</v>
       </c>
     </row>
     <row r="12">
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.27246819789088</v>
+        <v>15.4046032273367</v>
       </c>
       <c r="D12" t="n">
         <v>21.47965802121596</v>
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.78864650614645</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>15.60978849752428</v>
       </c>
     </row>
     <row r="14">
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.52062938288707</v>
+        <v>12.90605532002857</v>
       </c>
       <c r="D14" t="n">
         <v>14.44249047717483</v>
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.90016483380309</v>
+        <v>12.18348900970292</v>
       </c>
       <c r="D15" t="n">
         <v>12.541826921753</v>
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>11.98615772114931</v>
       </c>
       <c r="D16" t="n">
-        <v>9.506263020221864</v>
+        <v>9.092947236733956</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>31.03304493124168</v>
+        <v>29.42788743479814</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>2.675262494072558</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.473824288252715</v>
+        <v>3.556871932486194</v>
       </c>
       <c r="C2" t="n">
-        <v>5.101161071266427</v>
+        <v>5.15221195188726</v>
       </c>
       <c r="D2" t="n">
-        <v>14.03408343220815</v>
+        <v>17.96598298771663</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.43093048890212</v>
+        <v>15.15818455357075</v>
       </c>
       <c r="C3" t="n">
-        <v>21.32846887476196</v>
+        <v>19.24716374175872</v>
       </c>
       <c r="D3" t="n">
-        <v>52.71003424101125</v>
+        <v>73.90105843717866</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>47.36245449597887</v>
+        <v>42.9210278819663</v>
       </c>
       <c r="C4" t="n">
-        <v>82.30678228093984</v>
+        <v>80.20093345533043</v>
       </c>
       <c r="D4" t="n">
-        <v>105.5221702432642</v>
+        <v>161.7291898068026</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>60.30385273336034</v>
+        <v>56.25414345334224</v>
       </c>
       <c r="C5" t="n">
-        <v>176.2237129123025</v>
+        <v>181.5987815930538</v>
       </c>
       <c r="D5" t="n">
-        <v>99.1319744363217</v>
+        <v>147.3112430222339</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.79129831628549</v>
+        <v>43.75354993516761</v>
       </c>
       <c r="C6" t="n">
-        <v>236.1564650134576</v>
+        <v>249.0369948931757</v>
       </c>
       <c r="D6" t="n">
-        <v>57.43911293236815</v>
+        <v>77.20267596656069</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.09815907489146</v>
+        <v>18.44507586738907</v>
       </c>
       <c r="C7" t="n">
-        <v>211.5195063753838</v>
+        <v>216.4900950019854</v>
       </c>
       <c r="D7" t="n">
-        <v>38.20765715387736</v>
+        <v>42.22006002113408</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.425538724295373</v>
+        <v>5.424156065963627</v>
       </c>
       <c r="C8" t="n">
-        <v>145.2839340129642</v>
+        <v>147.9542877685155</v>
       </c>
       <c r="D8" t="n">
-        <v>33.88011327355743</v>
+        <v>33.29597338953057</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.662499773917349</v>
+        <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>69.0031191406913</v>
+        <v>66.45155685735384</v>
       </c>
       <c r="D9" t="n">
-        <v>33.28124717396686</v>
+        <v>32.28280975874785</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.423534171157875</v>
+        <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>33.59540643932586</v>
+        <v>31.74481201682062</v>
       </c>
       <c r="D10" t="n">
-        <v>25.48126166372597</v>
+        <v>24.62714116103124</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>25.23287949455151</v>
+        <v>23.63361248433346</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>23.63361248433346</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.65909686691488</v>
+        <v>17.57426565372215</v>
       </c>
       <c r="D12" t="n">
-        <v>21.91359050649305</v>
+        <v>21.69662426385451</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>16.1301147807751</v>
+        <v>15.34962535589888</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>15.60978849752428</v>
       </c>
     </row>
     <row r="14">
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>14.44249047717483</v>
+        <v>13.82791641431633</v>
       </c>
       <c r="D14" t="n">
         <v>14.44249047717483</v>
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>13.25850274585317</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>11.82515109765283</v>
       </c>
     </row>
     <row r="16">
@@ -3156,7 +3156,7 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>23.1456838753228</v>
       </c>
       <c r="D16" t="n">
         <v>8.266315669758143</v>
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34.94432778496098</v>
+        <v>33.52766584773283</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>4.249985811684442</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1.070104997629023</v>
+        <v>0.5350524988145117</v>
       </c>
       <c r="D18" t="n">
         <v>1.070104997629023</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.111158474758142</v>
+        <v>2.626175108860218</v>
       </c>
       <c r="C2" t="n">
-        <v>3.314380249537232</v>
+        <v>2.73318560862312</v>
       </c>
       <c r="D2" t="n">
-        <v>10.08549416572748</v>
+        <v>13.55400880483147</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.71916340332318</v>
+        <v>14.01935721664445</v>
       </c>
       <c r="C3" t="n">
-        <v>21.05357951757285</v>
+        <v>19.78221624057323</v>
       </c>
       <c r="D3" t="n">
-        <v>52.49895848459819</v>
+        <v>71.79030087304801</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.02312964320797</v>
+        <v>38.59446574935061</v>
       </c>
       <c r="C4" t="n">
-        <v>70.82033414125216</v>
+        <v>68.67619715517714</v>
       </c>
       <c r="D4" t="n">
-        <v>107.5514427479423</v>
+        <v>164.0009539944297</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>65.97344572538567</v>
+        <v>60.67200812245289</v>
       </c>
       <c r="C5" t="n">
-        <v>172.4194405583461</v>
+        <v>173.3275571847744</v>
       </c>
       <c r="D5" t="n">
-        <v>109.0230825566083</v>
+        <v>161.5220410412065</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>59.61270234957058</v>
+        <v>52.40765594810324</v>
       </c>
       <c r="C6" t="n">
-        <v>263.2458294167398</v>
+        <v>274.5162930614932</v>
       </c>
       <c r="D6" t="n">
-        <v>68.50831829775093</v>
+        <v>92.73981513397071</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.61906619521901</v>
+        <v>16.64847756861741</v>
       </c>
       <c r="C7" t="n">
-        <v>262.9022177202534</v>
+        <v>268.9507653261179</v>
       </c>
       <c r="D7" t="n">
-        <v>42.16017341117502</v>
+        <v>47.25053525769474</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.340707511102648</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C8" t="n">
-        <v>185.923380230261</v>
+        <v>188.9275282052562</v>
       </c>
       <c r="D8" t="n">
-        <v>35.71598148049896</v>
+        <v>34.29735604786232</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>1.664062358698343</v>
       </c>
       <c r="C9" t="n">
-        <v>83.86874287839649</v>
+        <v>74.88280614142545</v>
       </c>
       <c r="D9" t="n">
-        <v>32.9484347022272</v>
+        <v>32.17187226816797</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>34.73423377625215</v>
+        <v>32.31422568528377</v>
       </c>
       <c r="D10" t="n">
-        <v>26.1930287493049</v>
+        <v>25.0542014123786</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>24.87748682561417</v>
+        <v>23.27821981539612</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.22516438163779</v>
+        <v>16.92336692580652</v>
       </c>
       <c r="D12" t="n">
-        <v>20.39482680802324</v>
+        <v>19.96089432274615</v>
       </c>
     </row>
     <row r="13">
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.96750451476862</v>
+        <v>11.44717823151781</v>
       </c>
       <c r="D13" t="n">
         <v>16.3902779224005</v>
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.67690719431156</v>
+        <v>11.06233313145306</v>
       </c>
       <c r="D14" t="n">
-        <v>11.36962016288231</v>
+        <v>11.06233313145306</v>
       </c>
     </row>
     <row r="15">
@@ -3453,7 +3453,7 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>19.35024725070463</v>
       </c>
       <c r="D15" t="n">
         <v>6.808420328951629</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0.4722206457427158</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.839034434232529</v>
+        <v>3.597123588360313</v>
       </c>
       <c r="C2" t="n">
-        <v>4.055599766243573</v>
+        <v>6.382341825308514</v>
       </c>
       <c r="D2" t="n">
-        <v>10.24061030299848</v>
+        <v>14.9893239484403</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.55793579564845</v>
+        <v>11.53062678637879</v>
       </c>
       <c r="C3" t="n">
-        <v>17.14131491614931</v>
+        <v>15.44289138780233</v>
       </c>
       <c r="D3" t="n">
-        <v>48.78795216254525</v>
+        <v>66.70975650357076</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.89251614081414</v>
+        <v>33.20859784385261</v>
       </c>
       <c r="C4" t="n">
-        <v>62.24378619695202</v>
+        <v>59.9592592891697</v>
       </c>
       <c r="D4" t="n">
-        <v>108.7256130022215</v>
+        <v>162.2652240533213</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>65.50711556586843</v>
+        <v>59.54299826256906</v>
       </c>
       <c r="C5" t="n">
-        <v>153.520797251595</v>
+        <v>153.0790107846839</v>
       </c>
       <c r="D5" t="n">
-        <v>119.7732199181109</v>
+        <v>177.2790916943678</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>71.52719248830986</v>
+        <v>63.35610634586367</v>
       </c>
       <c r="C6" t="n">
-        <v>268.8005579273682</v>
+        <v>275.9251010170873</v>
       </c>
       <c r="D6" t="n">
-        <v>82.43539123019619</v>
+        <v>113.0266496945268</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>39.16584291322225</v>
+        <v>31.68001666834032</v>
       </c>
       <c r="C7" t="n">
-        <v>313.2668566958189</v>
+        <v>320.7526829407009</v>
       </c>
       <c r="D7" t="n">
-        <v>49.28667999630262</v>
+        <v>57.43125895073415</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.26555490623215</v>
+        <v>8.511752595819845</v>
       </c>
       <c r="C8" t="n">
-        <v>254.8518865454295</v>
+        <v>256.1870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>38.05254101660637</v>
+        <v>37.30150402285756</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.995312245657018</v>
+        <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>140.6687380552999</v>
+        <v>132.570301242968</v>
       </c>
       <c r="D9" t="n">
-        <v>34.16874709860598</v>
+        <v>33.05937219280708</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7117670855789376</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>57.79548734900973</v>
+        <v>51.24723016168351</v>
       </c>
       <c r="D10" t="n">
-        <v>27.75891633757857</v>
+        <v>26.1930287493049</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>30.56376952861169</v>
+        <v>27.8983245115816</v>
       </c>
       <c r="D11" t="n">
-        <v>24.87748682561417</v>
+        <v>24.52209415667683</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>21.47965802121596</v>
+        <v>19.7439280801076</v>
       </c>
       <c r="D12" t="n">
-        <v>20.82875929330033</v>
+        <v>20.39482680802324</v>
       </c>
     </row>
     <row r="13">
@@ -3736,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>14.04880964777186</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
         <v>16.65044106402591</v>
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12.29148125717007</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="D14" t="n">
-        <v>11.67690719431156</v>
+        <v>11.36962016288231</v>
       </c>
     </row>
     <row r="15">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>27.69215749368978</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>2.89321048441535</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.227806525114265</v>
+        <v>5.43888228152733</v>
       </c>
       <c r="C2" t="n">
-        <v>7.303221171892022</v>
+        <v>10.08451241802324</v>
       </c>
       <c r="D2" t="n">
-        <v>4.211697651218817</v>
+        <v>14.93729132011522</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.425317740117121</v>
+        <v>2.57316073283089</v>
       </c>
       <c r="C2" t="n">
-        <v>2.270782439922872</v>
+        <v>3.676645152404305</v>
       </c>
       <c r="D2" t="n">
-        <v>7.537858873207011</v>
+        <v>11.03288070032565</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.34395585385165</v>
+        <v>15.54106615822701</v>
       </c>
       <c r="C3" t="n">
-        <v>19.17844140246144</v>
+        <v>20.48907458763093</v>
       </c>
       <c r="D3" t="n">
-        <v>52.51859343868312</v>
+        <v>73.02730298039899</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>50.87220253866122</v>
+        <v>45.28213111067988</v>
       </c>
       <c r="C4" t="n">
-        <v>89.07102396320037</v>
+        <v>86.62058169340033</v>
       </c>
       <c r="D4" t="n">
-        <v>112.4523272875424</v>
+        <v>166.9874305107485</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.70602513473626</v>
+        <v>37.33095645398497</v>
       </c>
       <c r="C5" t="n">
-        <v>226.9555255292564</v>
+        <v>230.3425551089079</v>
       </c>
       <c r="D5" t="n">
-        <v>111.9928693619549</v>
+        <v>161.3993225781757</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>24.31200014796801</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="C6" t="n">
-        <v>264.2923724694669</v>
+        <v>265.338915522194</v>
       </c>
       <c r="D6" t="n">
-        <v>68.30706001838034</v>
+        <v>88.27188133194348</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.425939634922873</v>
+        <v>5.629341336151211</v>
       </c>
       <c r="C7" t="n">
-        <v>179.1807369974939</v>
+        <v>180.1389227568388</v>
       </c>
       <c r="D7" t="n">
-        <v>33.47661496711198</v>
+        <v>33.53650157707104</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>2.002765316663493</v>
+        <v>1.585522542358599</v>
       </c>
       <c r="C8" t="n">
-        <v>103.6431051373358</v>
+        <v>97.71825774220626</v>
       </c>
       <c r="D8" t="n">
-        <v>25.11801501315464</v>
+        <v>24.36697801940583</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4437499623195582</v>
+        <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>44.04218376021615</v>
+        <v>39.04999668412111</v>
       </c>
       <c r="D9" t="n">
-        <v>21.1890607007589</v>
+        <v>19.96874830438012</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>23.91537407545231</v>
+        <v>21.78007281871549</v>
       </c>
       <c r="D10" t="n">
-        <v>19.50241814486289</v>
+        <v>19.21771131063132</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>17.23654444346124</v>
+        <v>15.81497376771187</v>
       </c>
       <c r="D11" t="n">
-        <v>16.70345544005523</v>
+        <v>16.34806277111788</v>
       </c>
     </row>
     <row r="12">
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>11.28224461720434</v>
+        <v>10.63134588928871</v>
       </c>
       <c r="D12" t="n">
         <v>13.4519070435898</v>
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>10.14636252339079</v>
+        <v>9.626036240139976</v>
       </c>
       <c r="D13" t="n">
-        <v>9.626036240139976</v>
+        <v>9.365873098514571</v>
       </c>
     </row>
     <row r="14">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>24.72531593145592</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>2.150027472300515</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.397068040872216</v>
+        <v>7.060729488943061</v>
       </c>
       <c r="C2" t="n">
-        <v>3.624612524079224</v>
+        <v>5.771694753266998</v>
       </c>
       <c r="D2" t="n">
-        <v>8.912305659152546</v>
+        <v>26.85669019737574</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.10847527355266</v>
+        <v>11.55517047898496</v>
       </c>
       <c r="C3" t="n">
-        <v>18.69247628885927</v>
+        <v>25.41253932442869</v>
       </c>
       <c r="D3" t="n">
-        <v>6.842781498600269</v>
+        <v>15.6834195753428</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.493238258159399</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>4.736932672990861</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>9.449321653375552</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>8.050331174823848</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>18.27425176685013</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>32.8453511932813</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>32.21899615797182</v>
       </c>
     </row>
     <row r="8">
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>8.845546815263761</v>
       </c>
       <c r="C8" t="n">
         <v>21.69662426385451</v>
@@ -4610,7 +4610,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>8.764061755811273</v>
       </c>
       <c r="C9" t="n">
         <v>22.74218556887735</v>
@@ -4655,7 +4655,7 @@
         <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>25.60201663134832</v>
+        <v>25.81898287398687</v>
       </c>
       <c r="D12" t="n">
         <v>43.17628228507047</v>
@@ -4669,7 +4669,7 @@
         <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>24.19517217116264</v>
+        <v>23.93500902953724</v>
       </c>
       <c r="D13" t="n">
         <v>44.22773407631881</v>
@@ -4697,7 +4697,7 @@
         <v>5.375068680751286</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
         <v>42.28387362191012</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.3991291226621</v>
+        <v>13.39677461490428</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14838187746631</v>
+        <v>70.13605533685181</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576368132077894</v>
+        <v>1.576091131165209</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.759512870188536</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C2" t="n">
-        <v>5.502695882303372</v>
+        <v>5.662720758095602</v>
       </c>
       <c r="D2" t="n">
-        <v>9.899943849624835</v>
+        <v>30.56082428549896</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.68618489200629</v>
+        <v>19.22752878767378</v>
       </c>
       <c r="C3" t="n">
-        <v>15.80613803837365</v>
+        <v>23.59630607157209</v>
       </c>
       <c r="D3" t="n">
-        <v>12.67436286182632</v>
+        <v>34.44952694202058</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>12.96692367769187</v>
+        <v>13.49019520405542</v>
       </c>
       <c r="C4" t="n">
-        <v>29.48188355853172</v>
+        <v>39.27088991757666</v>
       </c>
       <c r="D4" t="n">
-        <v>18.65909686691488</v>
+        <v>23.29196428325558</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.399612373357458</v>
+        <v>5.522330836388309</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>29.40334374219198</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.366053024963819</v>
+        <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>16.50317890838889</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>34.57617239586842</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.641744203407924</v>
+        <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>24.07441720354028</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>34.97378021608837</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>9.513135254151592</v>
       </c>
       <c r="C8" t="n">
         <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>36.96770980341364</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>9.429686699290611</v>
       </c>
       <c r="C9" t="n">
-        <v>25.5156228333746</v>
+        <v>25.73749781453438</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>39.82655911818034</v>
       </c>
     </row>
     <row r="10">
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>8.825911861178826</v>
       </c>
       <c r="C10" t="n">
         <v>27.3318560862312</v>
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.463246047684251</v>
+        <v>7.640942382152923</v>
       </c>
       <c r="C11" t="n">
         <v>29.49759152179966</v>
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>29.07347651356504</v>
+        <v>28.8565102709265</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -4983,7 +4983,7 @@
         <v>26.79680358741669</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>44.74806035956962</v>
       </c>
     </row>
     <row r="14">
@@ -4994,10 +4994,10 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>25.81211064005714</v>
+        <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>44.86390658867074</v>
       </c>
     </row>
     <row r="15">
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5022,10 +5022,10 @@
         <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>36.36098972218912</v>
       </c>
     </row>
     <row r="18">
@@ -5050,7 +5050,7 @@
         <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>34.24335992412875</v>
       </c>
       <c r="D18" t="n">
         <v>31.56809743005619</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44491944371019</v>
+        <v>15.43538208140127</v>
       </c>
       <c r="C21" t="n">
-        <v>86.16639268596215</v>
+        <v>86.11318424360711</v>
       </c>
       <c r="D21" t="n">
-        <v>3.251561988149515</v>
+        <v>3.249554122400268</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.738896168399354</v>
+        <v>5.202281084803848</v>
       </c>
       <c r="C2" t="n">
-        <v>7.095090658591698</v>
+        <v>5.422192570555134</v>
       </c>
       <c r="D2" t="n">
-        <v>11.25475568148543</v>
+        <v>24.42980987247763</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.20021977840412</v>
+        <v>16.84679060487527</v>
       </c>
       <c r="C3" t="n">
-        <v>19.20298509506761</v>
+        <v>22.64891953697392</v>
       </c>
       <c r="D3" t="n">
-        <v>17.65182372235765</v>
+        <v>50.90361846519712</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.93835518327748</v>
+        <v>26.53369520267854</v>
       </c>
       <c r="C4" t="n">
-        <v>35.16129402759952</v>
+        <v>50.74457533710914</v>
       </c>
       <c r="D4" t="n">
-        <v>20.65008121112741</v>
+        <v>35.30168394930681</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>11.70734137314322</v>
+        <v>11.92823460659875</v>
       </c>
       <c r="C5" t="n">
-        <v>33.84575210390879</v>
+        <v>42.97600575340413</v>
       </c>
       <c r="D5" t="n">
-        <v>29.50151851261666</v>
+        <v>31.29320807286709</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.876741757621407</v>
+        <v>5.916993413495527</v>
       </c>
       <c r="C6" t="n">
-        <v>12.19625172985813</v>
+        <v>12.3572583533546</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>36.10573531908495</v>
       </c>
     </row>
     <row r="7">
@@ -5207,10 +5207,10 @@
         <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>24.25407703341745</v>
       </c>
       <c r="D7" t="n">
-        <v>37.42913122440964</v>
+        <v>37.4890178343687</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>10.34762080276138</v>
       </c>
       <c r="C8" t="n">
-        <v>29.6242369756475</v>
+        <v>29.54078842078653</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>38.13598957146735</v>
       </c>
     </row>
     <row r="9">
@@ -5235,10 +5235,10 @@
         <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>29.39843500367073</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>40.93593402397924</v>
       </c>
     </row>
     <row r="10">
@@ -5252,7 +5252,7 @@
         <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>49.68134257340984</v>
       </c>
     </row>
     <row r="11">
@@ -5266,7 +5266,7 @@
         <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>49.04418831335365</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.508987279156352</v>
+        <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>31.89403766786613</v>
       </c>
       <c r="D12" t="n">
-        <v>45.77987719673301</v>
+        <v>46.2138096820101</v>
       </c>
     </row>
     <row r="13">
@@ -5291,7 +5291,7 @@
         <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>29.65859814529614</v>
       </c>
       <c r="D13" t="n">
         <v>45.00822350119503</v>
@@ -5308,7 +5308,7 @@
         <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
         <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.35888735806038</v>
+        <v>43.71722527011046</v>
       </c>
     </row>
     <row r="16">
@@ -5333,7 +5333,7 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
         <v>40.91826256530281</v>
@@ -5361,10 +5361,10 @@
         <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>31.56809743005619</v>
       </c>
     </row>
     <row r="19">
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>36.71049190490098</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.74407690965828</v>
+        <v>16.72123597370103</v>
       </c>
       <c r="C21" t="n">
-        <v>102.1388691489155</v>
+        <v>101.9995394395763</v>
       </c>
       <c r="D21" t="n">
-        <v>5.023223072897484</v>
+        <v>4.180308993425259</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.756968537703296</v>
+        <v>6.046584110456105</v>
       </c>
       <c r="C2" t="n">
-        <v>4.074252972624263</v>
+        <v>4.883213080923635</v>
       </c>
       <c r="D2" t="n">
-        <v>18.76807086208628</v>
+        <v>26.02711338728719</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.67498475663207</v>
+        <v>17.32293824143497</v>
       </c>
       <c r="C3" t="n">
-        <v>24.1019061392592</v>
+        <v>21.71135047941821</v>
       </c>
       <c r="D3" t="n">
-        <v>22.27585540936013</v>
+        <v>58.14891652253858</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.37978179729005</v>
+        <v>29.82647700272235</v>
       </c>
       <c r="C4" t="n">
-        <v>42.49985811684442</v>
+        <v>53.9863062565321</v>
       </c>
       <c r="D4" t="n">
-        <v>24.42784637706914</v>
+        <v>51.91874559138832</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>24.83821691744431</v>
+        <v>25.40272184738622</v>
       </c>
       <c r="C5" t="n">
-        <v>50.63363784652926</v>
+        <v>69.43410638285567</v>
       </c>
       <c r="D5" t="n">
-        <v>30.4587225242573</v>
+        <v>36.34920874973816</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.86794708601219</v>
+        <v>10.90819874188631</v>
       </c>
       <c r="C6" t="n">
-        <v>34.49566908412018</v>
+        <v>41.21769561509809</v>
       </c>
       <c r="D6" t="n">
-        <v>37.75605320992383</v>
+        <v>38.19882142453915</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19985992550562</v>
+        <v>21.08008670558751</v>
       </c>
       <c r="D7" t="n">
-        <v>40.00425545264903</v>
+        <v>39.76470901281281</v>
       </c>
     </row>
     <row r="8">
@@ -5532,10 +5532,10 @@
         <v>10.76486357706628</v>
       </c>
       <c r="C8" t="n">
-        <v>31.79389940203295</v>
+        <v>31.54355373745002</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>39.55461500410399</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>33.9468721174462</v>
+        <v>33.83593462686631</v>
       </c>
       <c r="D9" t="n">
-        <v>41.93437143919824</v>
+        <v>42.04530892977813</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10.10709261522091</v>
+        <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.59540643932586</v>
+        <v>33.02599277086271</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>48.9695754878309</v>
       </c>
     </row>
     <row r="11">
@@ -5577,7 +5577,7 @@
         <v>33.93999988351647</v>
       </c>
       <c r="D11" t="n">
-        <v>50.46575898910303</v>
+        <v>50.28806265463436</v>
       </c>
     </row>
     <row r="12">
@@ -5588,10 +5588,10 @@
         <v>7.159886007071988</v>
       </c>
       <c r="C12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.49763257952867</v>
       </c>
       <c r="D12" t="n">
-        <v>47.29864089520282</v>
+        <v>47.08167465256428</v>
       </c>
     </row>
     <row r="13">
@@ -5602,7 +5602,7 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>32.5203927031756</v>
       </c>
       <c r="D13" t="n">
         <v>45.78871292607123</v>
@@ -5616,7 +5616,7 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.42141611149592</v>
       </c>
       <c r="D14" t="n">
         <v>45.7857676829585</v>
@@ -5630,10 +5630,10 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.02537087605695</v>
+        <v>29.38370878810703</v>
       </c>
       <c r="D15" t="n">
-        <v>44.07556318216055</v>
+        <v>43.71722527011046</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>41.33157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5672,10 +5672,10 @@
         <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
-        <v>32.63820242768521</v>
+        <v>32.1031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -5686,7 +5686,7 @@
         <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>36.71049190490098</v>
       </c>
       <c r="D19" t="n">
         <v>25.27607639353838</v>
@@ -5700,7 +5700,7 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.67733346713483</v>
+        <v>39.00483628972577</v>
       </c>
       <c r="D20" t="n">
         <v>16.13993225781756</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.07901822204694</v>
+        <v>18.03719568536482</v>
       </c>
       <c r="C21" t="n">
-        <v>117.9440712581158</v>
+        <v>117.6712289949991</v>
       </c>
       <c r="D21" t="n">
-        <v>6.887245036970263</v>
+        <v>6.012398561788273</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.466191290796993</v>
+        <v>6.701409829188727</v>
       </c>
       <c r="C2" t="n">
-        <v>4.941136195474197</v>
+        <v>9.100801218367932</v>
       </c>
       <c r="D2" t="n">
-        <v>23.70724356215198</v>
+        <v>26.60045404656733</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.47863521578271</v>
+        <v>17.00387023755476</v>
       </c>
       <c r="C3" t="n">
-        <v>18.13778883595982</v>
+        <v>18.90846078379357</v>
       </c>
       <c r="D3" t="n">
-        <v>29.70768553050848</v>
+        <v>61.15306449753382</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.56448923440869</v>
+        <v>22.93460811890974</v>
       </c>
       <c r="C4" t="n">
-        <v>44.13348629671111</v>
+        <v>45.24384295021426</v>
       </c>
       <c r="D4" t="n">
-        <v>25.76793199336603</v>
+        <v>59.71676760622073</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>21.47573103039898</v>
+        <v>21.3775562599743</v>
       </c>
       <c r="C5" t="n">
-        <v>48.64559874542947</v>
+        <v>62.88094045700822</v>
       </c>
       <c r="D5" t="n">
-        <v>26.38446955163304</v>
+        <v>37.13460691313561</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.23650338573225</v>
+        <v>12.3572583533546</v>
       </c>
       <c r="C6" t="n">
-        <v>40.05039759474864</v>
+        <v>51.92463607761381</v>
       </c>
       <c r="D6" t="n">
-        <v>30.02773528209295</v>
+        <v>31.83905979642831</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.509568116233099</v>
+        <v>5.389794896314989</v>
       </c>
       <c r="C7" t="n">
-        <v>22.99645822427728</v>
+        <v>25.63146906247572</v>
       </c>
       <c r="D7" t="n">
-        <v>31.38058361854505</v>
+        <v>30.9014907388726</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.69247628885927</v>
+        <v>18.60902773399829</v>
       </c>
       <c r="D8" t="n">
-        <v>30.12492830481337</v>
+        <v>29.87458264023044</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>22.07656062539802</v>
+        <v>21.74374815365835</v>
       </c>
       <c r="D9" t="n">
-        <v>30.28593492830985</v>
+        <v>30.17499743772996</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.412955930589413</v>
+        <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>21.21065915025234</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>33.31069960509428</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.61277479836603</v>
+        <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
-        <v>34.29539255245382</v>
+        <v>34.47308888692249</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>2.820561154301086</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>20.17786056538469</v>
       </c>
       <c r="D12" t="n">
-        <v>32.32797015314322</v>
+        <v>31.67707142522758</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>2.081305133003238</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
-        <v>30.17892442854696</v>
+        <v>30.43908757017236</v>
       </c>
     </row>
     <row r="14">
@@ -5927,10 +5927,10 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.8226478228966</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>29.49955501720816</v>
       </c>
     </row>
     <row r="15">
@@ -5955,10 +5955,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>15.29268398905256</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -5969,7 +5969,7 @@
         <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
         <v>23.61103228713579</v>
@@ -5983,7 +5983,7 @@
         <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>17.12167996206437</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -5997,10 +5997,10 @@
         <v>1.203622685406589</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.07001145283669</v>
+        <v>7.045815401621534</v>
       </c>
       <c r="C21" t="n">
-        <v>67.16510880194855</v>
+        <v>66.05451939020188</v>
       </c>
       <c r="D21" t="n">
-        <v>5.302508589627518</v>
+        <v>4.403634626013458</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.254313713128929</v>
+        <v>6.523713494720055</v>
       </c>
       <c r="C2" t="n">
-        <v>8.658033003752621</v>
+        <v>8.691412425697012</v>
       </c>
       <c r="D2" t="n">
-        <v>22.47024145480099</v>
+        <v>24.74102389472387</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.58510593619787</v>
+        <v>20.89159114637213</v>
       </c>
       <c r="C3" t="n">
-        <v>18.93791321492097</v>
+        <v>29.46715734296801</v>
       </c>
       <c r="D3" t="n">
-        <v>43.10363295495621</v>
+        <v>68.72233929727672</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.93308659185775</v>
+        <v>29.35425635697963</v>
       </c>
       <c r="C4" t="n">
-        <v>45.09069030835175</v>
+        <v>46.18828424169969</v>
       </c>
       <c r="D4" t="n">
-        <v>35.85048091598077</v>
+        <v>77.91640654754811</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.93701358267474</v>
+        <v>28.83883881225006</v>
       </c>
       <c r="C5" t="n">
-        <v>69.53228115328035</v>
+        <v>75.69274799742909</v>
       </c>
       <c r="D5" t="n">
-        <v>29.99239236474006</v>
+        <v>50.56000676871075</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>22.33966901013618</v>
+        <v>21.89690079552086</v>
       </c>
       <c r="C6" t="n">
-        <v>62.792583163626</v>
+        <v>80.26180181299375</v>
       </c>
       <c r="D6" t="n">
-        <v>32.24157635516951</v>
+        <v>36.95102009244145</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.89936301254809</v>
+        <v>10.65981657271187</v>
       </c>
       <c r="C7" t="n">
-        <v>44.13643153982385</v>
+        <v>54.43692845278139</v>
       </c>
       <c r="D7" t="n">
-        <v>33.65627479698915</v>
+        <v>33.29695513723482</v>
       </c>
     </row>
     <row r="8">
@@ -6154,10 +6154,10 @@
         <v>5.674501730546564</v>
       </c>
       <c r="C8" t="n">
-        <v>26.11939767148639</v>
+        <v>27.78836876870596</v>
       </c>
       <c r="D8" t="n">
-        <v>32.04424506661589</v>
+        <v>31.96079651175491</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>23.51874800293658</v>
+        <v>23.18593553119691</v>
       </c>
       <c r="D9" t="n">
-        <v>31.72812230584841</v>
+        <v>31.50624732468863</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.840016181936776</v>
+        <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>24.91184799526281</v>
+        <v>24.48478774391545</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>33.45305302221006</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
-        <v>34.82848155585983</v>
+        <v>35.18387422479719</v>
       </c>
     </row>
     <row r="12">
@@ -6213,7 +6213,7 @@
         <v>22.1305567491316</v>
       </c>
       <c r="D12" t="n">
-        <v>33.41280136633594</v>
+        <v>32.97886888105885</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>21.33337761328319</v>
+        <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>30.69925071179776</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>19.97365704290136</v>
+        <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -6252,7 +6252,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
         <v>28.66703296400686</v>
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -6280,10 +6280,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -6294,7 +6294,7 @@
         <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>17.12167996206437</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -6308,10 +6308,10 @@
         <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -6325,7 +6325,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.298723414582396</v>
+        <v>7.264158406326507</v>
       </c>
       <c r="C21" t="n">
-        <v>77.54893627993796</v>
+        <v>75.36564346563752</v>
       </c>
       <c r="D21" t="n">
-        <v>6.386382987759597</v>
+        <v>5.44811880474488</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.372704274715294</v>
+        <v>4.71238898038469</v>
       </c>
       <c r="C2" t="n">
-        <v>4.945063186291184</v>
+        <v>6.062292073724055</v>
       </c>
       <c r="D2" t="n">
-        <v>18.48140053244621</v>
+        <v>21.23323934745001</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.14546289114455</v>
+        <v>21.78007281871549</v>
       </c>
       <c r="C3" t="n">
-        <v>28.21542902005333</v>
+        <v>32.04424506661589</v>
       </c>
       <c r="D3" t="n">
-        <v>51.56138942704249</v>
+        <v>72.57079029792423</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.08395694314227</v>
+        <v>35.46759931132452</v>
       </c>
       <c r="C4" t="n">
-        <v>46.57116584635595</v>
+        <v>62.16720987602077</v>
       </c>
       <c r="D4" t="n">
-        <v>50.11920204950392</v>
+        <v>94.89082435397546</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.38004383919731</v>
+        <v>37.25732537616646</v>
       </c>
       <c r="C5" t="n">
-        <v>77.80350556155973</v>
+        <v>81.16599144860506</v>
       </c>
       <c r="D5" t="n">
-        <v>36.54555829058752</v>
+        <v>67.12699927787567</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.71830482880595</v>
+        <v>30.99377502307181</v>
       </c>
       <c r="C6" t="n">
-        <v>90.08320584627884</v>
+        <v>101.3134178351581</v>
       </c>
       <c r="D6" t="n">
-        <v>34.5359207399943</v>
+        <v>43.99505987041232</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.76258128648829</v>
+        <v>18.92416874706152</v>
       </c>
       <c r="C7" t="n">
-        <v>70.24699348197203</v>
+        <v>88.15308985972959</v>
       </c>
       <c r="D7" t="n">
-        <v>35.93196597543326</v>
+        <v>36.77037851486003</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.095892479846697</v>
+        <v>8.845546815263761</v>
       </c>
       <c r="C8" t="n">
-        <v>44.81187396034566</v>
+        <v>51.7381040138069</v>
       </c>
       <c r="D8" t="n">
-        <v>34.29735604786232</v>
+        <v>33.71321616383547</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>29.17656002251095</v>
+        <v>29.50937249425062</v>
       </c>
       <c r="D9" t="n">
-        <v>32.8374972116473</v>
+        <v>32.9484347022272</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>4.982369599052563</v>
       </c>
       <c r="C10" t="n">
-        <v>27.47420950334699</v>
+        <v>26.90479583488384</v>
       </c>
       <c r="D10" t="n">
-        <v>34.87658719336794</v>
+        <v>34.16482010778901</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>27.00984283923824</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>35.18387422479719</v>
+        <v>35.36157055926586</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.95111790343269</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>34.49763257952867</v>
+        <v>34.06370009425158</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>31.73990327829938</v>
+        <v>31.21957699504857</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>22.12466626290612</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -6563,7 +6563,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>19.35024725070463</v>
       </c>
       <c r="D15" t="n">
         <v>29.02537087605695</v>
@@ -6580,7 +6580,7 @@
         <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -6591,10 +6591,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -6605,7 +6605,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>17.12167996206437</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -6619,10 +6619,10 @@
         <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6636,7 +6636,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.516176058963037</v>
+        <v>7.469417461897959</v>
       </c>
       <c r="C21" t="n">
-        <v>87.37554668544529</v>
+        <v>84.03094644635205</v>
       </c>
       <c r="D21" t="n">
-        <v>7.516176058963037</v>
+        <v>6.535740279160715</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_65_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_65_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497643830257</v>
+        <v>10.8449764423267</v>
       </c>
       <c r="C21" t="n">
-        <v>37.789072311569</v>
+        <v>37.78907232559101</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.39648720379547</v>
+        <v>4.854742397500478</v>
       </c>
       <c r="C2" t="n">
-        <v>5.928774385946488</v>
+        <v>4.711407232680442</v>
       </c>
       <c r="D2" t="n">
-        <v>29.85592943384975</v>
+        <v>24.51424017504286</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.8691908756237</v>
+        <v>15.60978849752428</v>
       </c>
       <c r="C3" t="n">
-        <v>27.30731239362503</v>
+        <v>30.55198855616074</v>
       </c>
       <c r="D3" t="n">
-        <v>72.41371066524474</v>
+        <v>68.04493338134642</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.44131310748811</v>
+        <v>36.30993884156828</v>
       </c>
       <c r="C4" t="n">
-        <v>71.0373003838907</v>
+        <v>72.13489431723865</v>
       </c>
       <c r="D4" t="n">
-        <v>107.2961883448382</v>
+        <v>91.75119519579417</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.93950116189775</v>
+        <v>46.58392856651115</v>
       </c>
       <c r="C5" t="n">
-        <v>98.61655689159213</v>
+        <v>118.9387343695011</v>
       </c>
       <c r="D5" t="n">
-        <v>85.01935118777379</v>
+        <v>67.29880512611886</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.85543071223103</v>
+        <v>40.37241084174159</v>
       </c>
       <c r="C6" t="n">
-        <v>114.5159609618692</v>
+        <v>128.1210206473215</v>
       </c>
       <c r="D6" t="n">
-        <v>54.17872880656449</v>
+        <v>45.40386782600649</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>27.66761380108361</v>
+        <v>27.12863431145211</v>
       </c>
       <c r="C7" t="n">
-        <v>118.1562814492164</v>
+        <v>111.1495480840069</v>
       </c>
       <c r="D7" t="n">
-        <v>40.48334833232147</v>
+        <v>38.5669768136317</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.52004854581032</v>
+        <v>13.76901155206151</v>
       </c>
       <c r="C8" t="n">
-        <v>84.44993751931062</v>
+        <v>70.51402885752715</v>
       </c>
       <c r="D8" t="n">
-        <v>36.04977569994287</v>
+        <v>35.9663271450819</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.432811868852599</v>
+        <v>7.21093688769282</v>
       </c>
       <c r="C9" t="n">
-        <v>46.48280855297372</v>
+        <v>40.38124657107979</v>
       </c>
       <c r="D9" t="n">
-        <v>33.9468721174462</v>
+        <v>34.39062207976576</v>
       </c>
     </row>
     <row r="10">
@@ -895,10 +895,10 @@
         <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>31.60245859970483</v>
+        <v>30.46363126277853</v>
       </c>
       <c r="D10" t="n">
-        <v>34.87658719336794</v>
+        <v>35.01894061048373</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>28.96450251839364</v>
+        <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
-        <v>35.53926689373453</v>
+        <v>36.25005223160922</v>
       </c>
     </row>
     <row r="12">
@@ -923,7 +923,7 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.55471281509523</v>
+        <v>27.77167905773377</v>
       </c>
       <c r="D12" t="n">
         <v>34.93156506480576</v>
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.23582473766426</v>
+        <v>25.75615102091507</v>
       </c>
       <c r="D13" t="n">
-        <v>31.73990327829938</v>
+        <v>32.00006641992479</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>23.66110142005238</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -982,7 +982,7 @@
         <v>19.01252604044373</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -996,7 +996,7 @@
         <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1010,7 +1010,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1021,7 +1021,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
         <v>16.24890625298896</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.660526008721306</v>
+        <v>7.686087371135179</v>
       </c>
       <c r="C21" t="n">
-        <v>92.88387785574584</v>
+        <v>94.15457029640594</v>
       </c>
       <c r="D21" t="n">
-        <v>7.660526008721306</v>
+        <v>8.646848292527077</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.199155915241861</v>
+        <v>6.726935269499145</v>
       </c>
       <c r="C2" t="n">
-        <v>7.666467822463342</v>
+        <v>5.296528864411543</v>
       </c>
       <c r="D2" t="n">
-        <v>33.49330467808419</v>
+        <v>34.45443568054181</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.61317570899353</v>
+        <v>15.80613803837365</v>
       </c>
       <c r="C3" t="n">
-        <v>24.98547907308132</v>
+        <v>24.08717992369549</v>
       </c>
       <c r="D3" t="n">
-        <v>77.99985510240909</v>
+        <v>70.88709298514094</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.11399021134642</v>
+        <v>32.73637719810989</v>
       </c>
       <c r="C4" t="n">
-        <v>69.53129940557609</v>
+        <v>74.12587866145118</v>
       </c>
       <c r="D4" t="n">
-        <v>117.2383473457456</v>
+        <v>102.8547617308256</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>50.29002615004288</v>
+        <v>50.04458922398117</v>
       </c>
       <c r="C5" t="n">
-        <v>112.7537238327462</v>
+        <v>124.4365215132832</v>
       </c>
       <c r="D5" t="n">
-        <v>100.2364406035994</v>
+        <v>81.36234098945442</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.63029169278902</v>
+        <v>50.99884799250906</v>
       </c>
       <c r="C6" t="n">
-        <v>134.2392723401876</v>
+        <v>157.0619612208132</v>
       </c>
       <c r="D6" t="n">
-        <v>66.53598715991909</v>
+        <v>54.74225198880216</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>37.12969817461437</v>
+        <v>36.53083207502382</v>
       </c>
       <c r="C7" t="n">
-        <v>139.416027984681</v>
+        <v>145.0453693208322</v>
       </c>
       <c r="D7" t="n">
-        <v>45.51382356888213</v>
+        <v>42.04040019125691</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>21.61317570899353</v>
+        <v>20.77869016038374</v>
       </c>
       <c r="C8" t="n">
-        <v>117.3286681345363</v>
+        <v>106.814150222053</v>
       </c>
       <c r="D8" t="n">
-        <v>38.63668090063322</v>
+        <v>38.13598957146735</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>10.31718662392973</v>
       </c>
       <c r="C9" t="n">
-        <v>73.44061876388687</v>
+        <v>61.90311974357836</v>
       </c>
       <c r="D9" t="n">
-        <v>35.16718451382499</v>
+        <v>35.49999698556465</v>
       </c>
     </row>
     <row r="10">
@@ -1206,10 +1206,10 @@
         <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>42.13661146627311</v>
+        <v>39.00483628972578</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>35.87306111317846</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>32.87382187670443</v>
+        <v>32.34073287329842</v>
       </c>
       <c r="D11" t="n">
-        <v>35.7169632282032</v>
+        <v>36.42774856607789</v>
       </c>
     </row>
     <row r="12">
@@ -1234,7 +1234,7 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>29.94134148411922</v>
+        <v>30.8092064546734</v>
       </c>
       <c r="D12" t="n">
         <v>35.58246379272139</v>
@@ -1245,10 +1245,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>27.83745615391831</v>
+        <v>28.09761929554372</v>
       </c>
       <c r="D13" t="n">
         <v>32.5203927031756</v>
@@ -1262,10 +1262,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>24.89024954576939</v>
+        <v>25.81211064005714</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>31.34327720578367</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.25247339090745</v>
+        <v>20.66578917439536</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>18.41660518396592</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1321,7 +1321,7 @@
         <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1332,7 +1332,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
         <v>16.24890625298896</v>
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.83593805310645</v>
+        <v>7.865472318206693</v>
       </c>
       <c r="C21" t="n">
-        <v>100.8877024337455</v>
+        <v>102.251140136687</v>
       </c>
       <c r="D21" t="n">
-        <v>8.815430309744755</v>
+        <v>9.831840397758366</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.51331518060084</v>
+        <v>7.12552483742335</v>
       </c>
       <c r="C2" t="n">
-        <v>10.37707323388879</v>
+        <v>5.127668259281091</v>
       </c>
       <c r="D2" t="n">
-        <v>29.02831611916969</v>
+        <v>32.06878875922206</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
+        <v>18.56975782582842</v>
+      </c>
+      <c r="C3" t="n">
         <v>22.25131171675396</v>
       </c>
-      <c r="C3" t="n">
-        <v>27.22877257728529</v>
-      </c>
       <c r="D3" t="n">
-        <v>83.74307917225292</v>
+        <v>78.51527264713866</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.94356702143497</v>
+        <v>31.15379989886403</v>
       </c>
       <c r="C4" t="n">
-        <v>65.48551711637499</v>
+        <v>66.90217905360313</v>
       </c>
       <c r="D4" t="n">
-        <v>124.8576912784051</v>
+        <v>110.4613429433299</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52.0817157102933</v>
+        <v>49.3573658310084</v>
       </c>
       <c r="C5" t="n">
-        <v>117.9569866652543</v>
+        <v>128.289881252452</v>
       </c>
       <c r="D5" t="n">
-        <v>115.2080930933632</v>
+        <v>95.64677008624551</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>56.91584140600459</v>
+        <v>57.64037121173875</v>
       </c>
       <c r="C6" t="n">
-        <v>153.4795638480166</v>
+        <v>175.0544513965446</v>
       </c>
       <c r="D6" t="n">
-        <v>78.16871570753956</v>
+        <v>64.0403844957237</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>46.47200932822701</v>
+        <v>46.41212271826796</v>
       </c>
       <c r="C7" t="n">
-        <v>161.5740736695315</v>
+        <v>179.1208503875348</v>
       </c>
       <c r="D7" t="n">
-        <v>52.34089710421445</v>
+        <v>46.59178254814513</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>29.04009709162065</v>
+        <v>28.53940576245478</v>
       </c>
       <c r="C8" t="n">
-        <v>145.5342796775471</v>
+        <v>144.1156542449105</v>
       </c>
       <c r="D8" t="n">
-        <v>40.97324043674063</v>
+        <v>40.47254910757476</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15.08749871886498</v>
+        <v>14.75468624712531</v>
       </c>
       <c r="C9" t="n">
-        <v>104.0593661639364</v>
+        <v>91.0796797660893</v>
       </c>
       <c r="D9" t="n">
-        <v>36.83124687252333</v>
+        <v>36.72030938194344</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.829437941368314</v>
+        <v>7.687084524252525</v>
       </c>
       <c r="C10" t="n">
-        <v>60.07314202286233</v>
+        <v>53.24017800130454</v>
       </c>
       <c r="D10" t="n">
-        <v>35.87306111317846</v>
+        <v>36.72718161587318</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.330890034060179</v>
+        <v>5.153193699591506</v>
       </c>
       <c r="C11" t="n">
-        <v>39.27088991757665</v>
+        <v>38.02701557629594</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>36.60544490054656</v>
       </c>
     </row>
     <row r="12">
@@ -1548,7 +1548,7 @@
         <v>33.1958351236974</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>36.23336252063703</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>30.43908757017236</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>32.780555844801</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>27.04125876577415</v>
+        <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>31.65056423721292</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>24.72531593145592</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.49242074137117</v>
+        <v>21.90573652485908</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -1615,10 +1615,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>19.83326712119407</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1629,10 +1629,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1643,7 +1643,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
         <v>16.24890625298896</v>
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.995649956573629</v>
+        <v>8.028763996121233</v>
       </c>
       <c r="C21" t="n">
-        <v>108.9407306583157</v>
+        <v>110.395504946667</v>
       </c>
       <c r="D21" t="n">
-        <v>9.994562445717037</v>
+        <v>11.0395504946667</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.004769869800992</v>
+        <v>6.531567476354029</v>
       </c>
       <c r="C2" t="n">
-        <v>7.139269305282806</v>
+        <v>3.486186097780424</v>
       </c>
       <c r="D2" t="n">
-        <v>24.02631156603219</v>
+        <v>26.40803149653495</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>26.45810062945154</v>
+        <v>21.91260875878881</v>
       </c>
       <c r="C3" t="n">
-        <v>42.34768722268617</v>
+        <v>35.0582105186536</v>
       </c>
       <c r="D3" t="n">
-        <v>91.12582190818894</v>
+        <v>84.65610453720245</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.01493150420873</v>
+        <v>23.71313404837746</v>
       </c>
       <c r="C4" t="n">
-        <v>94.71214627180254</v>
+        <v>100.6468111439745</v>
       </c>
       <c r="D4" t="n">
-        <v>122.9049950946582</v>
+        <v>106.4793742549048</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.05406254365837</v>
+        <v>32.47130531796326</v>
       </c>
       <c r="C5" t="n">
-        <v>91.6952355766521</v>
+        <v>104.6052178874977</v>
       </c>
       <c r="D5" t="n">
-        <v>77.65624340592271</v>
+        <v>63.96086293167971</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.86043726174349</v>
+        <v>28.82018560586937</v>
       </c>
       <c r="C6" t="n">
-        <v>106.4253781311713</v>
+        <v>117.9776033670435</v>
       </c>
       <c r="D6" t="n">
-        <v>34.45541742824607</v>
+        <v>30.67176177607885</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.22360179685679</v>
+        <v>18.92416874706152</v>
       </c>
       <c r="C7" t="n">
-        <v>102.3462164200257</v>
+        <v>101.3281440507218</v>
       </c>
       <c r="D7" t="n">
-        <v>28.80545939030566</v>
+        <v>28.44613973055133</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>10.18072369303942</v>
       </c>
       <c r="C8" t="n">
-        <v>76.68922191723958</v>
+        <v>67.09263810822702</v>
       </c>
       <c r="D8" t="n">
-        <v>27.12078032981814</v>
+        <v>27.03733177495716</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.546874528994477</v>
+        <v>5.435937038414587</v>
       </c>
       <c r="C9" t="n">
-        <v>45.81718360949438</v>
+        <v>40.60312155223957</v>
       </c>
       <c r="D9" t="n">
-        <v>27.29062268265283</v>
+        <v>27.95624762613216</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.843542262126263</v>
+        <v>3.701188845010476</v>
       </c>
       <c r="C10" t="n">
-        <v>30.7483380970101</v>
+        <v>29.75186417719959</v>
       </c>
       <c r="D10" t="n">
-        <v>28.32833000604172</v>
+        <v>28.61303684027329</v>
       </c>
     </row>
     <row r="11">
@@ -1845,7 +1845,7 @@
         <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>28.43141351498762</v>
+        <v>28.96450251839364</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.169662426385451</v>
+        <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>24.30021917551705</v>
+        <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
-        <v>26.90381408717959</v>
+        <v>26.68684784454105</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>22.37403017978481</v>
+        <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>26.01631416254048</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>20.28094407433061</v>
+        <v>20.58823110575986</v>
       </c>
       <c r="D14" t="n">
-        <v>24.89024954576939</v>
+        <v>23.96838845148163</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>18.27523351455437</v>
       </c>
       <c r="D15" t="n">
-        <v>22.21695054710532</v>
+        <v>22.93362637120549</v>
       </c>
     </row>
     <row r="16">
@@ -1912,10 +1912,10 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>16.94594712300419</v>
       </c>
       <c r="D16" t="n">
-        <v>20.25247339090745</v>
+        <v>20.66578917439536</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>15.58328130950962</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>17.47216389248049</v>
       </c>
     </row>
     <row r="18">
@@ -1940,7 +1940,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>15.51652246562084</v>
+        <v>16.05157496443535</v>
       </c>
       <c r="D18" t="n">
         <v>13.9113649691773</v>
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
       <c r="D19" t="n">
         <v>9.027170140549421</v>
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>73.30219233758808</v>
+        <v>73.97468951499715</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>7.397468951499714</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.225442119078272</v>
+        <v>3.977059949903829</v>
       </c>
       <c r="C2" t="n">
-        <v>3.522510762837555</v>
+        <v>2.178498155723672</v>
       </c>
       <c r="D2" t="n">
-        <v>17.66654993792135</v>
+        <v>18.12993485432585</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>26.08503650183775</v>
+        <v>22.77163800000477</v>
       </c>
       <c r="C3" t="n">
-        <v>35.70125526493526</v>
+        <v>24.41115666609694</v>
       </c>
       <c r="D3" t="n">
-        <v>90.69385291832035</v>
+        <v>86.22199212547612</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.90153179660161</v>
+        <v>31.65154598491717</v>
       </c>
       <c r="C4" t="n">
-        <v>103.4673722982756</v>
+        <v>97.94111447107029</v>
       </c>
       <c r="D4" t="n">
-        <v>136.7653091832146</v>
+        <v>122.7390797326405</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.00559705325178</v>
+        <v>35.51472320112837</v>
       </c>
       <c r="C5" t="n">
-        <v>130.6460757426443</v>
+        <v>144.145106676038</v>
       </c>
       <c r="D5" t="n">
-        <v>96.57943040527999</v>
+        <v>80.79783605951251</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.37491411649783</v>
+        <v>34.77743067523902</v>
       </c>
       <c r="C6" t="n">
-        <v>126.6317093799791</v>
+        <v>142.5311134502562</v>
       </c>
       <c r="D6" t="n">
-        <v>43.9548082145382</v>
+        <v>38.31957639216151</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.96598298771663</v>
+        <v>17.84620976779852</v>
       </c>
       <c r="C7" t="n">
-        <v>126.1212005737707</v>
+        <v>130.5528097107408</v>
       </c>
       <c r="D7" t="n">
-        <v>31.9794497181356</v>
+        <v>31.02126395879071</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>8.511752595819845</v>
       </c>
       <c r="C8" t="n">
-        <v>97.88515485192822</v>
+        <v>88.70581381722054</v>
       </c>
       <c r="D8" t="n">
-        <v>27.87181732356695</v>
+        <v>28.28906009787184</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.659374604355361</v>
+        <v>4.548437113775471</v>
       </c>
       <c r="C9" t="n">
-        <v>51.03124566674919</v>
+        <v>46.81562102471339</v>
       </c>
       <c r="D9" t="n">
-        <v>28.28906009787183</v>
+        <v>28.84374755077128</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>32.74128593663113</v>
+        <v>32.31422568528377</v>
       </c>
       <c r="D10" t="n">
-        <v>29.60951076008381</v>
+        <v>30.03657101143117</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
-        <v>29.31989518733098</v>
+        <v>29.67528785626833</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>20.61179305066178</v>
+        <v>21.26269177857742</v>
       </c>
       <c r="D12" t="n">
-        <v>28.20561154301086</v>
+        <v>28.42257778564941</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.65044106402591</v>
+        <v>16.91060420565131</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>25.49598787928967</v>
       </c>
     </row>
     <row r="14">
@@ -2198,7 +2198,7 @@
         <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>18.4372218857551</v>
+        <v>19.0517959486136</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>14.33351648200343</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>13.22610507161303</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -2237,7 +2237,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.22217808079604</v>
+        <v>13.69439872653876</v>
       </c>
       <c r="D17" t="n">
         <v>11.8055161435679</v>
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>13.9113649691773</v>
+        <v>14.44641746799181</v>
       </c>
       <c r="D18" t="n">
         <v>7.490734983403163</v>
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>63.79200232654924</v>
+        <v>64.39381366925254</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>6.018113427032947</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.684900044665779</v>
+        <v>3.75813021185679</v>
       </c>
       <c r="C2" t="n">
-        <v>6.71024555852695</v>
+        <v>5.127668259281091</v>
       </c>
       <c r="D2" t="n">
-        <v>16.22239906497429</v>
+        <v>16.48354395430395</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.20927649192059</v>
+        <v>18.08870145074748</v>
       </c>
       <c r="C3" t="n">
-        <v>23.97918767622835</v>
+        <v>15.77668560724624</v>
       </c>
       <c r="D3" t="n">
-        <v>84.2732229325462</v>
+        <v>81.75504007115313</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.65301075870693</v>
+        <v>37.62449901755476</v>
       </c>
       <c r="C4" t="n">
-        <v>96.10328276872026</v>
+        <v>79.62661104834605</v>
       </c>
       <c r="D4" t="n">
-        <v>148.7622661291107</v>
+        <v>135.5528507684698</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.95775345765094</v>
+        <v>41.20885988575987</v>
       </c>
       <c r="C5" t="n">
-        <v>161.301147807751</v>
+        <v>161.9392838155114</v>
       </c>
       <c r="D5" t="n">
-        <v>119.1841712955628</v>
+        <v>101.3899941560894</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.69442408873454</v>
+        <v>40.89568236810514</v>
       </c>
       <c r="C6" t="n">
-        <v>164.1060009987841</v>
+        <v>184.8758554298296</v>
       </c>
       <c r="D6" t="n">
-        <v>59.81396062894117</v>
+        <v>52.60891422747383</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>27.06874770149305</v>
+        <v>27.42806736124739</v>
       </c>
       <c r="C7" t="n">
-        <v>154.1481340346087</v>
+        <v>165.5864765367883</v>
       </c>
       <c r="D7" t="n">
-        <v>36.23139902522853</v>
+        <v>34.2551408965797</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.60073178400781</v>
+        <v>12.51728322914683</v>
       </c>
       <c r="C8" t="n">
-        <v>130.0128484734051</v>
+        <v>127.8431860470196</v>
       </c>
       <c r="D8" t="n">
-        <v>29.70768553050848</v>
+        <v>29.87458264023044</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.990624491314035</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>80.87343063273947</v>
+        <v>74.88280614142545</v>
       </c>
       <c r="D9" t="n">
-        <v>29.28749751309084</v>
+        <v>29.50937249425062</v>
       </c>
     </row>
     <row r="10">
@@ -2450,10 +2450,10 @@
         <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
-        <v>44.55661955724149</v>
+        <v>42.13661146627311</v>
       </c>
       <c r="D10" t="n">
-        <v>29.89421759431538</v>
+        <v>30.7483380970101</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>33.22921454564179</v>
+        <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
-        <v>29.852984190737</v>
+        <v>30.20837685967435</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>25.16808414607123</v>
+        <v>25.60201663134832</v>
       </c>
       <c r="D12" t="n">
-        <v>28.63954402828795</v>
+        <v>28.8565102709265</v>
       </c>
     </row>
     <row r="13">
@@ -2495,7 +2495,7 @@
         <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
-        <v>26.53664044579129</v>
+        <v>26.27647730416588</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.28621266575034</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>19.35908298004286</v>
       </c>
     </row>
     <row r="15">
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.40853021815369</v>
+        <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
         <v>17.20021977840412</v>
@@ -2537,7 +2537,7 @@
         <v>14.46605242207675</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.16661937228147</v>
+        <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>11.33329549782518</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.3032465340878</v>
+        <v>34.9050578767911</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>4.212679398923063</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.77638250760998</v>
+        <v>2.244275251908209</v>
       </c>
       <c r="C2" t="n">
-        <v>3.145519644406781</v>
+        <v>2.363066724122073</v>
       </c>
       <c r="D2" t="n">
-        <v>11.37256540599505</v>
+        <v>11.38630987385451</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.41053477129119</v>
+        <v>17.61255381418778</v>
       </c>
       <c r="C3" t="n">
-        <v>26.46300936797277</v>
+        <v>18.66302385773187</v>
       </c>
       <c r="D3" t="n">
-        <v>82.05447312094842</v>
+        <v>79.86517574047804</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>46.37972504402781</v>
+        <v>41.61923042613503</v>
       </c>
       <c r="C4" t="n">
-        <v>92.29999216246813</v>
+        <v>73.39840361260428</v>
       </c>
       <c r="D4" t="n">
-        <v>158.0407636819473</v>
+        <v>147.128637949244</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.33220024359647</v>
+        <v>43.34416114249668</v>
       </c>
       <c r="C5" t="n">
-        <v>192.00530725807</v>
+        <v>183.9795197758523</v>
       </c>
       <c r="D5" t="n">
-        <v>125.4428129101362</v>
+        <v>107.3050240741764</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.32837106377072</v>
+        <v>33.65038431076368</v>
       </c>
       <c r="C6" t="n">
-        <v>197.3538687508066</v>
+        <v>222.3098953927605</v>
       </c>
       <c r="D6" t="n">
-        <v>58.12339108222817</v>
+        <v>51.52211951887262</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.324238784308704</v>
+        <v>8.26435217434965</v>
       </c>
       <c r="C7" t="n">
-        <v>164.2689711176891</v>
+        <v>171.4553643127757</v>
       </c>
       <c r="D7" t="n">
-        <v>35.81219275551515</v>
+        <v>34.37491411649782</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.088979188187965</v>
+        <v>4.005530633326986</v>
       </c>
       <c r="C8" t="n">
-        <v>99.05343461998193</v>
+        <v>95.2148010963769</v>
       </c>
       <c r="D8" t="n">
-        <v>31.37665662772806</v>
+        <v>31.54355373745002</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>33.9468721174462</v>
+        <v>32.17187226816797</v>
       </c>
       <c r="D9" t="n">
-        <v>31.39530983410874</v>
+        <v>32.06093477758807</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>26.05067533218912</v>
+        <v>26.33538216642069</v>
       </c>
       <c r="D10" t="n">
-        <v>23.34596040698915</v>
+        <v>23.63066724122073</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>20.07968579496001</v>
+        <v>20.43507846389736</v>
       </c>
       <c r="D11" t="n">
-        <v>22.92282714645877</v>
+        <v>23.10052348092744</v>
       </c>
     </row>
     <row r="12">
@@ -2792,7 +2792,7 @@
         <v>15.4046032273367</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>21.26269177857742</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>13.52848336452105</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12.90605532002857</v>
+        <v>13.21334235145782</v>
       </c>
       <c r="D14" t="n">
         <v>14.44249047717483</v>
@@ -2834,7 +2834,7 @@
         <v>12.18348900970292</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>12.18348900970292</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>11.98615772114931</v>
+        <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>9.506263020221864</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.27768003604838</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.42788743479814</v>
+        <v>29.96293993361265</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>3.21031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.556871932486194</v>
+        <v>2.821542902005333</v>
       </c>
       <c r="C2" t="n">
-        <v>5.15221195188726</v>
+        <v>3.114103717870883</v>
       </c>
       <c r="D2" t="n">
-        <v>17.96598298771663</v>
+        <v>15.16407503979623</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.15818455357075</v>
+        <v>12.772537632251</v>
       </c>
       <c r="C3" t="n">
-        <v>19.24716374175872</v>
+        <v>13.77882902910398</v>
       </c>
       <c r="D3" t="n">
-        <v>73.90105843717866</v>
+        <v>71.37796683726434</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.9210278819663</v>
+        <v>38.2881604656256</v>
       </c>
       <c r="C4" t="n">
-        <v>80.20093345533043</v>
+        <v>60.63568345739575</v>
       </c>
       <c r="D4" t="n">
-        <v>161.7291898068026</v>
+        <v>152.5272685748972</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>56.25414345334224</v>
+        <v>51.76264770641309</v>
       </c>
       <c r="C5" t="n">
-        <v>181.5987815930538</v>
+        <v>160.8102739556276</v>
       </c>
       <c r="D5" t="n">
-        <v>147.3112430222339</v>
+        <v>132.045066221196</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>43.75354993516761</v>
+        <v>43.39128503230054</v>
       </c>
       <c r="C6" t="n">
-        <v>249.0369948931757</v>
+        <v>258.8583989264608</v>
       </c>
       <c r="D6" t="n">
-        <v>77.20267596656069</v>
+        <v>67.54227855677206</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.44507586738907</v>
+        <v>18.86428213710246</v>
       </c>
       <c r="C7" t="n">
-        <v>216.4900950019854</v>
+        <v>237.0312022179414</v>
       </c>
       <c r="D7" t="n">
-        <v>42.22006002113408</v>
+        <v>39.70482240285375</v>
       </c>
     </row>
     <row r="8">
@@ -3044,10 +3044,10 @@
         <v>5.424156065963627</v>
       </c>
       <c r="C8" t="n">
-        <v>147.9542877685155</v>
+        <v>151.4591270726767</v>
       </c>
       <c r="D8" t="n">
-        <v>33.29597338953057</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -3058,10 +3058,10 @@
         <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>66.45155685735384</v>
+        <v>63.23436963053704</v>
       </c>
       <c r="D9" t="n">
-        <v>32.28280975874785</v>
+        <v>33.28124717396686</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>31.74481201682062</v>
+        <v>31.60245859970483</v>
       </c>
       <c r="D10" t="n">
-        <v>24.62714116103124</v>
+        <v>24.76949457814703</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>23.63361248433346</v>
+        <v>24.16670148773948</v>
       </c>
       <c r="D11" t="n">
-        <v>23.63361248433346</v>
+        <v>23.81130881880213</v>
       </c>
     </row>
     <row r="12">
@@ -3100,7 +3100,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.57426565372215</v>
+        <v>17.7912318963607</v>
       </c>
       <c r="D12" t="n">
         <v>21.69662426385451</v>
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>15.34962535589888</v>
+        <v>15.86995163914969</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -3131,7 +3131,7 @@
         <v>13.82791641431633</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>14.13520344574558</v>
       </c>
     </row>
     <row r="15">
@@ -3156,7 +3156,7 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.1456838753228</v>
+        <v>23.55899965881071</v>
       </c>
       <c r="D16" t="n">
         <v>8.266315669758143</v>
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.52766584773283</v>
+        <v>34.47210713921825</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="D18" t="n">
         <v>1.070104997629023</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.626175108860218</v>
+        <v>1.997856578142259</v>
       </c>
       <c r="C2" t="n">
-        <v>2.73318560862312</v>
+        <v>1.987057353395544</v>
       </c>
       <c r="D2" t="n">
-        <v>13.55400880483147</v>
+        <v>10.82573193472958</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.01935721664445</v>
+        <v>11.56989669454866</v>
       </c>
       <c r="C3" t="n">
-        <v>19.78221624057323</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="D3" t="n">
-        <v>71.79030087304801</v>
+        <v>68.02529842726149</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.59446574935061</v>
+        <v>33.88502201207866</v>
       </c>
       <c r="C4" t="n">
-        <v>68.67619715517714</v>
+        <v>50.87220253866122</v>
       </c>
       <c r="D4" t="n">
-        <v>164.0009539944297</v>
+        <v>153.7907778702628</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>60.67200812245289</v>
+        <v>55.54237636776331</v>
       </c>
       <c r="C5" t="n">
-        <v>173.3275571847744</v>
+        <v>145.9613399288945</v>
       </c>
       <c r="D5" t="n">
-        <v>161.5220410412065</v>
+        <v>149.1274762750905</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>52.40765594810324</v>
+        <v>51.4818678629985</v>
       </c>
       <c r="C6" t="n">
-        <v>274.5162930614932</v>
+        <v>271.2559089356895</v>
       </c>
       <c r="D6" t="n">
-        <v>92.73981513397071</v>
+        <v>80.90582830697966</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.64847756861741</v>
+        <v>17.72643654788041</v>
       </c>
       <c r="C7" t="n">
-        <v>268.9507653261179</v>
+        <v>290.9291511810913</v>
       </c>
       <c r="D7" t="n">
-        <v>47.25053525769474</v>
+        <v>44.49575119957818</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.422773407631881</v>
+        <v>4.506221962492859</v>
       </c>
       <c r="C8" t="n">
-        <v>188.9275282052562</v>
+        <v>197.8565235753809</v>
       </c>
       <c r="D8" t="n">
-        <v>34.29735604786232</v>
+        <v>34.88149593188918</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.664062358698343</v>
+        <v>1.774999849278233</v>
       </c>
       <c r="C9" t="n">
-        <v>74.88280614142545</v>
+        <v>74.32811868852599</v>
       </c>
       <c r="D9" t="n">
-        <v>32.17187226816797</v>
+        <v>33.05937219280708</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>32.31422568528377</v>
+        <v>32.74128593663113</v>
       </c>
       <c r="D10" t="n">
-        <v>25.0542014123786</v>
+        <v>25.19655482949439</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>23.63361248433346</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.92336692580652</v>
+        <v>17.57426565372215</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>20.17786056538469</v>
       </c>
     </row>
     <row r="13">
@@ -3428,7 +3428,7 @@
         <v>11.44717823151781</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>16.1301147807751</v>
       </c>
     </row>
     <row r="14">
@@ -3453,7 +3453,7 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
         <v>6.808420328951629</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.51878906066559</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
         <v>0.4722206457427158</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.597123588360313</v>
+        <v>3.837651775900782</v>
       </c>
       <c r="C2" t="n">
-        <v>6.382341825308514</v>
+        <v>4.443390109421064</v>
       </c>
       <c r="D2" t="n">
-        <v>14.9893239484403</v>
+        <v>23.08579726536374</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.53062678637879</v>
+        <v>9.24315463548372</v>
       </c>
       <c r="C3" t="n">
-        <v>15.44289138780233</v>
+        <v>10.66178006812036</v>
       </c>
       <c r="D3" t="n">
-        <v>66.70975650357076</v>
+        <v>62.43424525157591</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.20859784385261</v>
+        <v>28.52467954689108</v>
       </c>
       <c r="C4" t="n">
-        <v>59.9592592891697</v>
+        <v>42.72958707963818</v>
       </c>
       <c r="D4" t="n">
-        <v>162.2652240533213</v>
+        <v>150.9574539958066</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>59.54299826256906</v>
+        <v>53.75068680751288</v>
       </c>
       <c r="C5" t="n">
-        <v>153.0790107846839</v>
+        <v>123.0375310347315</v>
       </c>
       <c r="D5" t="n">
-        <v>177.2790916943678</v>
+        <v>165.6944687842554</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>63.35610634586367</v>
+        <v>60.6994970581718</v>
       </c>
       <c r="C6" t="n">
-        <v>275.9251010170873</v>
+        <v>256.3627962622654</v>
       </c>
       <c r="D6" t="n">
-        <v>113.0266496945268</v>
+        <v>101.8366893615217</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>31.68001666834032</v>
+        <v>32.63820242768521</v>
       </c>
       <c r="C7" t="n">
-        <v>320.7526829407009</v>
+        <v>333.807963911775</v>
       </c>
       <c r="D7" t="n">
-        <v>57.43125895073415</v>
+        <v>53.65840252331367</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.511752595819845</v>
+        <v>9.179341034707678</v>
       </c>
       <c r="C8" t="n">
-        <v>256.1870634232051</v>
+        <v>274.9629882669254</v>
       </c>
       <c r="D8" t="n">
-        <v>37.30150402285756</v>
+        <v>37.63529824230147</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>2.551562283337459</v>
       </c>
       <c r="C9" t="n">
-        <v>132.570301242968</v>
+        <v>137.8953007908027</v>
       </c>
       <c r="D9" t="n">
-        <v>33.05937219280708</v>
+        <v>34.05780960802609</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.7117670855789376</v>
       </c>
       <c r="C10" t="n">
-        <v>51.24723016168351</v>
+        <v>51.95899724726245</v>
       </c>
       <c r="D10" t="n">
-        <v>26.1930287493049</v>
+        <v>26.76244241776806</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>27.8983245115816</v>
+        <v>28.43141351498762</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>24.34439782220815</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>20.61179305066178</v>
       </c>
       <c r="D12" t="n">
-        <v>20.39482680802324</v>
+        <v>20.61179305066178</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>13.52848336452105</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>27.69215749368978</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.43888228152733</v>
+        <v>4.91561075516378</v>
       </c>
       <c r="C2" t="n">
-        <v>10.08451241802324</v>
+        <v>6.857507714163971</v>
       </c>
       <c r="D2" t="n">
-        <v>14.93729132011522</v>
+        <v>7.555530331883452</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.57316073283089</v>
+        <v>2.712568906833937</v>
       </c>
       <c r="C2" t="n">
-        <v>3.676645152404305</v>
+        <v>2.487748682561417</v>
       </c>
       <c r="D2" t="n">
-        <v>11.03288070032565</v>
+        <v>16.99110751739954</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.54106615822701</v>
+        <v>13.17505419099219</v>
       </c>
       <c r="C3" t="n">
-        <v>20.48907458763093</v>
+        <v>14.33842522052466</v>
       </c>
       <c r="D3" t="n">
-        <v>73.02730298039899</v>
+        <v>71.22579594310609</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>45.28213111067988</v>
+        <v>40.10046672766521</v>
       </c>
       <c r="C4" t="n">
-        <v>86.62058169340033</v>
+        <v>63.2520410892135</v>
       </c>
       <c r="D4" t="n">
-        <v>166.9874305107485</v>
+        <v>154.6203546803514</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.33095645398497</v>
+        <v>36.17740290149497</v>
       </c>
       <c r="C5" t="n">
-        <v>230.3425551089079</v>
+        <v>202.5100076935109</v>
       </c>
       <c r="D5" t="n">
-        <v>161.3993225781757</v>
+        <v>151.3118649170397</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>19.64280806657019</v>
+        <v>20.24658290468198</v>
       </c>
       <c r="C6" t="n">
-        <v>265.338915522194</v>
+        <v>272.6244652354096</v>
       </c>
       <c r="D6" t="n">
-        <v>88.27188133194348</v>
+        <v>80.62406671586082</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.629341336151211</v>
+        <v>6.048547605864599</v>
       </c>
       <c r="C7" t="n">
-        <v>180.1389227568388</v>
+        <v>193.37386355779</v>
       </c>
       <c r="D7" t="n">
-        <v>33.53650157707104</v>
+        <v>33.29695513723482</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.585522542358599</v>
+        <v>1.752419652080557</v>
       </c>
       <c r="C8" t="n">
-        <v>97.71825774220626</v>
+        <v>101.6403398206723</v>
       </c>
       <c r="D8" t="n">
-        <v>24.36697801940583</v>
+        <v>25.03456645829366</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3328124717396686</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>39.04999668412111</v>
+        <v>39.60468413702056</v>
       </c>
       <c r="D9" t="n">
-        <v>19.96874830438012</v>
+        <v>20.41249826669968</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>21.78007281871549</v>
+        <v>22.20713307006285</v>
       </c>
       <c r="D10" t="n">
-        <v>19.21771131063132</v>
+        <v>19.07535789351553</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.81497376771187</v>
+        <v>16.52575910558656</v>
       </c>
       <c r="D11" t="n">
-        <v>16.34806277111788</v>
+        <v>16.52575910558656</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.63134588928871</v>
+        <v>10.84831213192725</v>
       </c>
       <c r="D12" t="n">
-        <v>13.4519070435898</v>
+        <v>13.23494080095125</v>
       </c>
     </row>
     <row r="13">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>23.29196428325557</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.060729488943061</v>
+        <v>6.142795385472292</v>
       </c>
       <c r="C2" t="n">
-        <v>5.771694753266998</v>
+        <v>4.41982816451914</v>
       </c>
       <c r="D2" t="n">
-        <v>26.85669019737574</v>
+        <v>11.64549126777566</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.55517047898496</v>
+        <v>10.44579557318606</v>
       </c>
       <c r="C3" t="n">
-        <v>25.41253932442869</v>
+        <v>17.27875959474386</v>
       </c>
       <c r="D3" t="n">
-        <v>15.6834195753428</v>
+        <v>9.483682823024187</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.454950097693773</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>4.68784528777852</v>
       </c>
       <c r="C5" t="n">
-        <v>9.449321653375552</v>
+        <v>9.424777960769381</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>8.130834486572086</v>
       </c>
       <c r="C6" t="n">
-        <v>18.27425176685013</v>
+        <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>32.52333794628834</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>32.69808903764427</v>
       </c>
     </row>
     <row r="8">
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.845546815263761</v>
+        <v>8.762098260402782</v>
       </c>
       <c r="C8" t="n">
         <v>21.69662426385451</v>
@@ -4610,7 +4610,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.764061755811273</v>
+        <v>8.874999246391162</v>
       </c>
       <c r="C9" t="n">
         <v>22.74218556887735</v>
@@ -4697,7 +4697,7 @@
         <v>5.375068680751286</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>26.15866757965626</v>
       </c>
       <c r="D15" t="n">
         <v>42.28387362191012</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39677461490428</v>
+        <v>13.39868422151458</v>
       </c>
       <c r="C21" t="n">
-        <v>70.13605533685181</v>
+        <v>70.14605268910573</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576091131165209</v>
+        <v>1.576315790766421</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.339324852770901</v>
+        <v>4.445353604829558</v>
       </c>
       <c r="C2" t="n">
-        <v>5.662720758095602</v>
+        <v>8.579493187412876</v>
       </c>
       <c r="D2" t="n">
-        <v>30.56082428549896</v>
+        <v>28.08092958457152</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.22752878767378</v>
+        <v>16.89096925156637</v>
       </c>
       <c r="C3" t="n">
-        <v>23.59630607157209</v>
+        <v>17.26403337918016</v>
       </c>
       <c r="D3" t="n">
-        <v>34.44952694202058</v>
+        <v>16.97441780642735</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>13.49019520405542</v>
+        <v>12.22668590868978</v>
       </c>
       <c r="C4" t="n">
-        <v>39.27088991757666</v>
+        <v>27.28669569183585</v>
       </c>
       <c r="D4" t="n">
-        <v>23.29196428325558</v>
+        <v>20.0374706436774</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.522330836388309</v>
+        <v>5.399612373357458</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>29.10881943091793</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>7.366053024963819</v>
       </c>
       <c r="C6" t="n">
-        <v>16.50317890838889</v>
+        <v>16.54343056426301</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>34.77743067523902</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>9.641744203407924</v>
       </c>
       <c r="C7" t="n">
-        <v>24.07441720354028</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>35.27321326588365</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.513135254151592</v>
+        <v>9.596583809012571</v>
       </c>
       <c r="C8" t="n">
         <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.96770980341364</v>
+        <v>36.80081269369168</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>9.318749208710722</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>25.5156228333746</v>
       </c>
       <c r="D9" t="n">
-        <v>39.82655911818034</v>
+        <v>40.27030908049991</v>
       </c>
     </row>
     <row r="10">
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>8.968265278294615</v>
       </c>
       <c r="C10" t="n">
         <v>27.3318560862312</v>
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
         <v>29.49759152179966</v>
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>28.8565102709265</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -4983,7 +4983,7 @@
         <v>26.79680358741669</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>44.22773407631881</v>
       </c>
     </row>
     <row r="14">
@@ -4997,7 +4997,7 @@
         <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>5.0167307687012</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5022,10 +5022,10 @@
         <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>40.5049467818149</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5050,7 +5050,7 @@
         <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>31.56809743005619</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43538208140127</v>
+        <v>15.44368414724701</v>
       </c>
       <c r="C21" t="n">
-        <v>86.11318424360711</v>
+        <v>86.15950103200962</v>
       </c>
       <c r="D21" t="n">
-        <v>3.249554122400268</v>
+        <v>3.251301925736211</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.202281084803848</v>
+        <v>5.725552611167398</v>
       </c>
       <c r="C2" t="n">
-        <v>5.422192570555134</v>
+        <v>7.899142028369836</v>
       </c>
       <c r="D2" t="n">
-        <v>24.42980987247763</v>
+        <v>23.02591065540469</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.84679060487527</v>
+        <v>16.05157496443535</v>
       </c>
       <c r="C3" t="n">
-        <v>22.64891953697392</v>
+        <v>27.04224051347839</v>
       </c>
       <c r="D3" t="n">
-        <v>50.90361846519712</v>
+        <v>35.49999698556466</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.53369520267854</v>
+        <v>23.73865948868787</v>
       </c>
       <c r="C4" t="n">
-        <v>50.74457533710914</v>
+        <v>36.68005772606933</v>
       </c>
       <c r="D4" t="n">
-        <v>35.30168394930681</v>
+        <v>24.04496477241288</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>11.92823460659875</v>
+        <v>11.1428364432013</v>
       </c>
       <c r="C5" t="n">
-        <v>42.97600575340413</v>
+        <v>31.02322745419922</v>
       </c>
       <c r="D5" t="n">
-        <v>31.29320807286709</v>
+        <v>29.64878066825368</v>
       </c>
     </row>
     <row r="6">
@@ -5193,10 +5193,10 @@
         <v>5.916993413495527</v>
       </c>
       <c r="C6" t="n">
-        <v>12.3572583533546</v>
+        <v>12.11574841810989</v>
       </c>
       <c r="D6" t="n">
-        <v>36.10573531908495</v>
+        <v>36.6290068454485</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>9.521970983489814</v>
       </c>
       <c r="C7" t="n">
-        <v>24.25407703341745</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>37.42913122440964</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.34762080276138</v>
+        <v>10.51451791248334</v>
       </c>
       <c r="C8" t="n">
-        <v>29.54078842078653</v>
+        <v>29.87458264023044</v>
       </c>
       <c r="D8" t="n">
-        <v>38.13598957146735</v>
+        <v>38.55323234577224</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>9.984374152190059</v>
       </c>
       <c r="C9" t="n">
-        <v>29.39843500367073</v>
+        <v>29.62030998483051</v>
       </c>
       <c r="D9" t="n">
-        <v>40.93593402397924</v>
+        <v>41.26874649571891</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>9.537678946757763</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>29.46715734296802</v>
       </c>
       <c r="D10" t="n">
-        <v>49.68134257340984</v>
+        <v>49.25428232206248</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>8.174031385558941</v>
       </c>
       <c r="C11" t="n">
         <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
-        <v>49.04418831335365</v>
+        <v>49.75497365122833</v>
       </c>
     </row>
     <row r="12">
@@ -5277,7 +5277,7 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>31.89403766786613</v>
+        <v>32.11100391050467</v>
       </c>
       <c r="D12" t="n">
         <v>46.2138096820101</v>
@@ -5291,10 +5291,10 @@
         <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>29.65859814529614</v>
+        <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>44.48789721794422</v>
       </c>
     </row>
     <row r="14">
@@ -5305,10 +5305,10 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>27.65583282863265</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>45.7857676829585</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
         <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>43.35888735806038</v>
       </c>
     </row>
     <row r="16">
@@ -5333,7 +5333,7 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
         <v>40.91826256530281</v>
@@ -5347,10 +5347,10 @@
         <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.72123597370103</v>
+        <v>16.73793981377011</v>
       </c>
       <c r="C21" t="n">
-        <v>101.9995394395763</v>
+        <v>102.1014328639977</v>
       </c>
       <c r="D21" t="n">
-        <v>4.180308993425259</v>
+        <v>5.021381944131034</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.046584110456105</v>
+        <v>6.014186436215961</v>
       </c>
       <c r="C2" t="n">
-        <v>4.883213080923635</v>
+        <v>5.477170441992955</v>
       </c>
       <c r="D2" t="n">
-        <v>26.02711338728719</v>
+        <v>26.34225440035042</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.32293824143497</v>
+        <v>18.01016163440774</v>
       </c>
       <c r="C3" t="n">
-        <v>21.71135047941821</v>
+        <v>29.11372816943916</v>
       </c>
       <c r="D3" t="n">
-        <v>58.14891652253858</v>
+        <v>45.10148953309847</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.82647700272235</v>
+        <v>27.83549265850982</v>
       </c>
       <c r="C4" t="n">
         <v>53.9863062565321</v>
       </c>
       <c r="D4" t="n">
-        <v>51.91874559138832</v>
+        <v>35.76114187489431</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>25.40272184738622</v>
+        <v>23.26742059064941</v>
       </c>
       <c r="C5" t="n">
-        <v>69.43410638285567</v>
+        <v>50.56000676871075</v>
       </c>
       <c r="D5" t="n">
-        <v>36.34920874973816</v>
+        <v>31.31775176547326</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.90819874188631</v>
+        <v>10.58618549489336</v>
       </c>
       <c r="C6" t="n">
-        <v>41.21769561509809</v>
+        <v>31.67805317293184</v>
       </c>
       <c r="D6" t="n">
-        <v>38.19882142453915</v>
+        <v>38.15856976866503</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>8.563785224144926</v>
       </c>
       <c r="C7" t="n">
-        <v>21.08008670558751</v>
+        <v>21.19985992550562</v>
       </c>
       <c r="D7" t="n">
-        <v>39.76470901281281</v>
+        <v>39.46527596301753</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>10.93176068678823</v>
       </c>
       <c r="C8" t="n">
         <v>31.54355373745002</v>
       </c>
       <c r="D8" t="n">
-        <v>39.55461500410399</v>
+        <v>40.38910055271378</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>10.6499990956694</v>
       </c>
       <c r="C9" t="n">
-        <v>33.83593462686631</v>
+        <v>34.27968458918587</v>
       </c>
       <c r="D9" t="n">
-        <v>42.04530892977813</v>
+        <v>41.93437143919824</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.02599277086271</v>
+        <v>33.16834618797849</v>
       </c>
       <c r="D10" t="n">
-        <v>48.9695754878309</v>
+        <v>49.25428232206248</v>
       </c>
     </row>
     <row r="11">
@@ -5574,10 +5574,10 @@
         <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.93999988351647</v>
+        <v>33.40691088011046</v>
       </c>
       <c r="D11" t="n">
-        <v>50.28806265463436</v>
+        <v>50.82115165804038</v>
       </c>
     </row>
     <row r="12">
@@ -5588,7 +5588,7 @@
         <v>7.159886007071988</v>
       </c>
       <c r="C12" t="n">
-        <v>34.49763257952867</v>
+        <v>34.71459882216721</v>
       </c>
       <c r="D12" t="n">
         <v>47.08167465256428</v>
@@ -5602,10 +5602,10 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>32.5203927031756</v>
+        <v>33.30088212805181</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>45.52854978444583</v>
       </c>
     </row>
     <row r="14">
@@ -5619,7 +5619,7 @@
         <v>30.42141611149592</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.38370878810703</v>
+        <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>44.07556318216055</v>
       </c>
     </row>
     <row r="16">
@@ -5644,7 +5644,7 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
         <v>41.33157834879071</v>
@@ -5658,10 +5658,10 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -5672,7 +5672,7 @@
         <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
         <v>32.1031499288707</v>
@@ -5686,10 +5686,10 @@
         <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
-        <v>25.27607639353838</v>
+        <v>24.67426505083508</v>
       </c>
     </row>
     <row r="20">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.03719568536482</v>
+        <v>18.06479365701439</v>
       </c>
       <c r="C21" t="n">
-        <v>117.6712289949991</v>
+        <v>117.8512729052844</v>
       </c>
       <c r="D21" t="n">
-        <v>6.012398561788273</v>
+        <v>6.881826155053102</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.701409829188727</v>
+        <v>6.8791061636574</v>
       </c>
       <c r="C2" t="n">
-        <v>9.100801218367932</v>
+        <v>10.83947640258903</v>
       </c>
       <c r="D2" t="n">
-        <v>26.60045404656733</v>
+        <v>29.37781830188155</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.00387023755476</v>
+        <v>17.3278469799562</v>
       </c>
       <c r="C3" t="n">
-        <v>18.90846078379357</v>
+        <v>23.12506717353362</v>
       </c>
       <c r="D3" t="n">
-        <v>61.15306449753382</v>
+        <v>51.82646130718912</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.93460811890974</v>
+        <v>22.98565899953057</v>
       </c>
       <c r="C4" t="n">
-        <v>45.24384295021426</v>
+        <v>54.02459441699773</v>
       </c>
       <c r="D4" t="n">
-        <v>59.71676760622073</v>
+        <v>43.24009588584652</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>21.3775562599743</v>
+        <v>20.10128424445345</v>
       </c>
       <c r="C5" t="n">
-        <v>62.88094045700822</v>
+        <v>56.79410469067799</v>
       </c>
       <c r="D5" t="n">
-        <v>37.13460691313561</v>
+        <v>29.57514959043517</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.3572583533546</v>
+        <v>11.43147026824986</v>
       </c>
       <c r="C6" t="n">
-        <v>51.92463607761381</v>
+        <v>38.7220929509027</v>
       </c>
       <c r="D6" t="n">
-        <v>31.83905979642831</v>
+        <v>30.75226508782709</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.389794896314989</v>
+        <v>5.329908286355933</v>
       </c>
       <c r="C7" t="n">
-        <v>25.63146906247572</v>
+        <v>21.4992929753009</v>
       </c>
       <c r="D7" t="n">
-        <v>30.9014907388726</v>
+        <v>30.72183090899544</v>
       </c>
     </row>
     <row r="8">
@@ -5846,7 +5846,7 @@
         <v>18.60902773399829</v>
       </c>
       <c r="D8" t="n">
-        <v>29.87458264023044</v>
+        <v>30.37527396939631</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>21.74374815365835</v>
+        <v>21.85468564423824</v>
       </c>
       <c r="D9" t="n">
-        <v>30.17499743772996</v>
+        <v>29.95312245657017</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>4.412955930589413</v>
       </c>
       <c r="C10" t="n">
-        <v>21.21065915025234</v>
+        <v>21.49536598448391</v>
       </c>
       <c r="D10" t="n">
-        <v>33.31069960509428</v>
+        <v>33.73775985644164</v>
       </c>
     </row>
     <row r="11">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.820561154301086</v>
+        <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
-        <v>31.67707142522758</v>
+        <v>32.11100391050467</v>
       </c>
     </row>
     <row r="13">
@@ -5910,10 +5910,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.081305133003238</v>
+        <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>19.25207248027995</v>
       </c>
       <c r="D13" t="n">
         <v>30.43908757017236</v>
@@ -5927,7 +5927,7 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
         <v>29.49955501720816</v>
@@ -5944,7 +5944,7 @@
         <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -5955,10 +5955,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>15.29268398905256</v>
+        <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -5969,7 +5969,7 @@
         <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
         <v>23.61103228713579</v>
@@ -5980,10 +5980,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -5997,7 +5997,7 @@
         <v>1.203622685406589</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
         <v>15.64709491028566</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.045815401621534</v>
+        <v>7.060483038199038</v>
       </c>
       <c r="C21" t="n">
-        <v>66.05451939020188</v>
+        <v>66.19202848311598</v>
       </c>
       <c r="D21" t="n">
-        <v>4.403634626013458</v>
+        <v>5.295362278649279</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.523713494720055</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C2" t="n">
-        <v>8.691412425697012</v>
+        <v>6.021058670145687</v>
       </c>
       <c r="D2" t="n">
-        <v>24.74102389472387</v>
+        <v>21.86155787816798</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.89159114637213</v>
+        <v>21.51990967709008</v>
       </c>
       <c r="C3" t="n">
-        <v>29.46715734296801</v>
+        <v>35.52944941669207</v>
       </c>
       <c r="D3" t="n">
-        <v>68.72233929727672</v>
+        <v>63.98049788576463</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.35425635697963</v>
+        <v>29.92857876396402</v>
       </c>
       <c r="C4" t="n">
-        <v>46.18828424169969</v>
+        <v>56.58990116819465</v>
       </c>
       <c r="D4" t="n">
-        <v>77.91640654754811</v>
+        <v>59.94649656901449</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.83883881225006</v>
+        <v>28.66703296400687</v>
       </c>
       <c r="C5" t="n">
-        <v>75.69274799742909</v>
+        <v>83.17857424231102</v>
       </c>
       <c r="D5" t="n">
-        <v>50.56000676871075</v>
+        <v>39.46625771072178</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>21.89690079552086</v>
+        <v>20.40758952817845</v>
       </c>
       <c r="C6" t="n">
-        <v>80.26180181299375</v>
+        <v>68.66932492124741</v>
       </c>
       <c r="D6" t="n">
-        <v>36.95102009244145</v>
+        <v>33.6906359666378</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.65981657271187</v>
+        <v>10.18072369303942</v>
       </c>
       <c r="C7" t="n">
-        <v>54.43692845278139</v>
+        <v>41.98051358129786</v>
       </c>
       <c r="D7" t="n">
-        <v>33.29695513723482</v>
+        <v>32.87774886752143</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.674501730546564</v>
+        <v>5.591053175685585</v>
       </c>
       <c r="C8" t="n">
-        <v>27.78836876870596</v>
+        <v>24.78422079371073</v>
       </c>
       <c r="D8" t="n">
-        <v>31.96079651175491</v>
+        <v>32.3780392860598</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
-        <v>23.18593553119691</v>
+        <v>23.2968730217768</v>
       </c>
       <c r="D9" t="n">
-        <v>31.50624732468863</v>
+        <v>31.17343485294896</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>4.840016181936776</v>
       </c>
       <c r="C10" t="n">
-        <v>24.48478774391545</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>33.45305302221006</v>
+        <v>34.16482010778901</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>22.92282714645877</v>
+        <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
-        <v>35.18387422479719</v>
+        <v>35.36157055926586</v>
       </c>
     </row>
     <row r="12">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>21.07321447165778</v>
+        <v>21.33337761328319</v>
       </c>
       <c r="D13" t="n">
-        <v>30.69925071179776</v>
+        <v>31.21957699504857</v>
       </c>
     </row>
     <row r="14">
@@ -6252,7 +6252,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
         <v>28.66703296400686</v>
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -6280,7 +6280,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
         <v>24.0832529328785</v>
@@ -6294,10 +6294,10 @@
         <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>1.203622685406589</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.264158406326507</v>
+        <v>7.282365504383439</v>
       </c>
       <c r="C21" t="n">
-        <v>75.36564346563752</v>
+        <v>75.55454210797819</v>
       </c>
       <c r="D21" t="n">
-        <v>5.44811880474488</v>
+        <v>6.372069816335509</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.71238898038469</v>
+        <v>3.783655652167207</v>
       </c>
       <c r="C2" t="n">
-        <v>6.062292073724055</v>
+        <v>8.383143646563514</v>
       </c>
       <c r="D2" t="n">
-        <v>21.23323934745001</v>
+        <v>21.67011707583984</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.78007281871549</v>
+        <v>18.78574232076272</v>
       </c>
       <c r="C3" t="n">
-        <v>32.04424506661589</v>
+        <v>28.19088532744716</v>
       </c>
       <c r="D3" t="n">
-        <v>72.57079029792423</v>
+        <v>66.62139921018856</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.46759931132452</v>
+        <v>36.87149852839745</v>
       </c>
       <c r="C4" t="n">
-        <v>62.16720987602077</v>
+        <v>75.6701678002314</v>
       </c>
       <c r="D4" t="n">
-        <v>94.89082435397546</v>
+        <v>78.54177983515332</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.25732537616646</v>
+        <v>37.33095645398497</v>
       </c>
       <c r="C5" t="n">
-        <v>81.16599144860506</v>
+        <v>95.47496423800231</v>
       </c>
       <c r="D5" t="n">
-        <v>67.12699927787567</v>
+        <v>51.71356032120075</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.99377502307181</v>
+        <v>30.51075515258238</v>
       </c>
       <c r="C6" t="n">
-        <v>101.3134178351581</v>
+        <v>102.963735725997</v>
       </c>
       <c r="D6" t="n">
-        <v>43.99505987041232</v>
+        <v>38.84284791852506</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.92416874706152</v>
+        <v>17.66654993792135</v>
       </c>
       <c r="C7" t="n">
-        <v>88.15308985972959</v>
+        <v>73.78030346955629</v>
       </c>
       <c r="D7" t="n">
-        <v>36.77037851486003</v>
+        <v>35.2133266559246</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.845546815263761</v>
+        <v>8.678649705541805</v>
       </c>
       <c r="C8" t="n">
-        <v>51.7381040138069</v>
+        <v>41.8911745402114</v>
       </c>
       <c r="D8" t="n">
-        <v>33.71321616383547</v>
+        <v>34.38080460272329</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>5.546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>29.50937249425062</v>
+        <v>27.95624762613216</v>
       </c>
       <c r="D9" t="n">
-        <v>32.9484347022272</v>
+        <v>32.72655972106742</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
         <v>26.90479583488384</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>34.30717352490479</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.29905750136355</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -6521,7 +6521,7 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>24.95111790343269</v>
       </c>
       <c r="D12" t="n">
         <v>34.06370009425158</v>
@@ -6535,10 +6535,10 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>23.41468274628643</v>
       </c>
       <c r="D13" t="n">
-        <v>31.21957699504857</v>
+        <v>31.47974013667398</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
         <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -6566,7 +6566,7 @@
         <v>19.35024725070463</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -6591,10 +6591,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -6605,10 +6605,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6619,7 +6619,7 @@
         <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
         <v>16.24890625298896</v>
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
         <v>19.50241814486288</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.469417461897959</v>
+        <v>7.491539869930473</v>
       </c>
       <c r="C21" t="n">
-        <v>84.03094644635205</v>
+        <v>85.21626602045913</v>
       </c>
       <c r="D21" t="n">
-        <v>6.535740279160715</v>
+        <v>7.491539869930473</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_65_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_65_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.8449764423267</v>
+        <v>10.84497627297164</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907232559101</v>
+        <v>37.78907173547717</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.854742397500478</v>
+        <v>1.20951317163207</v>
       </c>
       <c r="C2" t="n">
-        <v>4.711407232680442</v>
+        <v>3.046363126277853</v>
       </c>
       <c r="D2" t="n">
-        <v>24.51424017504286</v>
+        <v>23.53249247079605</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.60978849752428</v>
+        <v>10.11691009226338</v>
       </c>
       <c r="C3" t="n">
-        <v>30.55198855616074</v>
+        <v>37.01188845010475</v>
       </c>
       <c r="D3" t="n">
-        <v>68.04493338134642</v>
+        <v>85.87347169046851</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.30993884156828</v>
+        <v>21.07125097624929</v>
       </c>
       <c r="C4" t="n">
-        <v>72.13489431723865</v>
+        <v>113.7924129038393</v>
       </c>
       <c r="D4" t="n">
-        <v>91.75119519579417</v>
+        <v>88.5222269965264</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.58392856651115</v>
+        <v>23.66011967234813</v>
       </c>
       <c r="C5" t="n">
-        <v>118.9387343695011</v>
+        <v>128.1671627894211</v>
       </c>
       <c r="D5" t="n">
-        <v>67.29880512611886</v>
+        <v>51.19814277647117</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.37241084174159</v>
+        <v>15.25537757629119</v>
       </c>
       <c r="C6" t="n">
-        <v>128.1210206473215</v>
+        <v>87.46684821446109</v>
       </c>
       <c r="D6" t="n">
-        <v>45.40386782600649</v>
+        <v>30.3497485290859</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>27.12863431145211</v>
+        <v>6.347980655659875</v>
       </c>
       <c r="C7" t="n">
-        <v>111.1495480840069</v>
+        <v>43.35790561035613</v>
       </c>
       <c r="D7" t="n">
-        <v>38.5669768136317</v>
+        <v>29.64387192973244</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.76901155206151</v>
+        <v>6.00829594999048</v>
       </c>
       <c r="C8" t="n">
-        <v>70.51402885752715</v>
+        <v>28.95664853675967</v>
       </c>
       <c r="D8" t="n">
-        <v>35.9663271450819</v>
+        <v>30.29182541453534</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.21093688769282</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>40.38124657107979</v>
+        <v>30.84062238120929</v>
       </c>
       <c r="D9" t="n">
-        <v>34.39062207976576</v>
+        <v>35.49999698556465</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.409429850399925</v>
+        <v>3.558835427894688</v>
       </c>
       <c r="C10" t="n">
-        <v>30.46363126277853</v>
+        <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
-        <v>35.01894061048373</v>
+        <v>37.15424186722054</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>31.09685853201771</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>37.49392657288993</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>27.77167905773377</v>
+        <v>23.64932044760141</v>
       </c>
       <c r="D12" t="n">
-        <v>34.93156506480576</v>
+        <v>37.75212621910684</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>25.75615102091507</v>
+        <v>20.03256190515617</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>36.16267668593127</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>23.66110142005238</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>27.04125876577415</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>25.44199175555609</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
+        <v>24.55547357862122</v>
+      </c>
+      <c r="D17" t="n">
         <v>17.9443845382232</v>
-      </c>
-      <c r="D17" t="n">
-        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>26.21757244191107</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>11.77115497391926</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>10.83260416865931</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>84.25358797846125</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.686087371135179</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>94.15457029640594</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.646848292527077</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.726935269499145</v>
+        <v>1.16042578641973</v>
       </c>
       <c r="C2" t="n">
-        <v>5.296528864411543</v>
+        <v>10.62251015995049</v>
       </c>
       <c r="D2" t="n">
-        <v>34.45443568054181</v>
+        <v>20.95245950403543</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.80613803837365</v>
+        <v>6.965499961631121</v>
       </c>
       <c r="C3" t="n">
-        <v>24.08717992369549</v>
+        <v>22.81090790817464</v>
       </c>
       <c r="D3" t="n">
-        <v>70.88709298514094</v>
+        <v>84.65610453720245</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.73637719810989</v>
+        <v>20.49692856926491</v>
       </c>
       <c r="C4" t="n">
-        <v>74.12587866145118</v>
+        <v>102.1528121222891</v>
       </c>
       <c r="D4" t="n">
-        <v>102.8547617308256</v>
+        <v>110.3975293425538</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>50.04458922398117</v>
+        <v>27.83254741539708</v>
       </c>
       <c r="C5" t="n">
-        <v>124.4365215132832</v>
+        <v>172.8612270252572</v>
       </c>
       <c r="D5" t="n">
-        <v>81.36234098945442</v>
+        <v>70.19496085364696</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>50.99884799250906</v>
+        <v>23.14470212761856</v>
       </c>
       <c r="C6" t="n">
-        <v>157.0619612208132</v>
+        <v>146.3147691024234</v>
       </c>
       <c r="D6" t="n">
-        <v>54.74225198880216</v>
+        <v>38.96360288614742</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>36.53083207502382</v>
+        <v>11.37845589222053</v>
       </c>
       <c r="C7" t="n">
-        <v>145.0453693208322</v>
+        <v>83.72148072275949</v>
       </c>
       <c r="D7" t="n">
-        <v>42.04040019125691</v>
+        <v>31.62013005838127</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>20.77869016038374</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>106.814150222053</v>
+        <v>42.72566008882119</v>
       </c>
       <c r="D8" t="n">
-        <v>38.13598957146735</v>
+        <v>31.46010518258904</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.31718662392973</v>
+        <v>6.212499472473814</v>
       </c>
       <c r="C9" t="n">
-        <v>61.90311974357836</v>
+        <v>34.50155957034565</v>
       </c>
       <c r="D9" t="n">
-        <v>35.49999698556465</v>
+        <v>36.0546844384641</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.26355035309465</v>
+        <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>39.00483628972578</v>
+        <v>33.88011327355743</v>
       </c>
       <c r="D10" t="n">
-        <v>35.87306111317846</v>
+        <v>37.5813021185679</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>32.34073287329842</v>
+        <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
-        <v>36.42774856607789</v>
+        <v>38.20471191076462</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>30.8092064546734</v>
+        <v>28.20561154301086</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>38.61999118966103</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>28.09761929554372</v>
+        <v>22.63419332141022</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>36.42283982755666</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>25.81211064005714</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>28.5776939229204</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>25.083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.66578917439536</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>21.49242074137117</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>26.44435616159209</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>16.99994324673777</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>8.560839981032187</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>51.36503988619312</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>9.63094497866121</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>45.13585070274711</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.865472318206693</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>102.251140136687</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9.831840397758366</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.12552483742335</v>
+        <v>0.6391177554646735</v>
       </c>
       <c r="C2" t="n">
-        <v>5.127668259281091</v>
+        <v>4.624031687002477</v>
       </c>
       <c r="D2" t="n">
-        <v>32.06878875922206</v>
+        <v>14.26184889959342</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.56975782582842</v>
+        <v>6.410812508731673</v>
       </c>
       <c r="C3" t="n">
-        <v>22.25131171675396</v>
+        <v>32.90327430783185</v>
       </c>
       <c r="D3" t="n">
-        <v>78.51527264713866</v>
+        <v>84.90154146326417</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.15379989886403</v>
+        <v>22.34752299177014</v>
       </c>
       <c r="C4" t="n">
-        <v>66.90217905360313</v>
+        <v>94.76319715242337</v>
       </c>
       <c r="D4" t="n">
-        <v>110.4613429433299</v>
+        <v>123.9132499869197</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.3573658310084</v>
+        <v>28.24979018970198</v>
       </c>
       <c r="C5" t="n">
-        <v>128.289881252452</v>
+        <v>201.7736969153258</v>
       </c>
       <c r="D5" t="n">
-        <v>95.64677008624551</v>
+        <v>79.88971943308421</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>57.64037121173875</v>
+        <v>17.10695374650067</v>
       </c>
       <c r="C6" t="n">
-        <v>175.0544513965446</v>
+        <v>180.9714448100401</v>
       </c>
       <c r="D6" t="n">
-        <v>64.0403844957237</v>
+        <v>39.32586778901449</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>46.41212271826796</v>
+        <v>4.311835917051991</v>
       </c>
       <c r="C7" t="n">
-        <v>179.1208503875348</v>
+        <v>78.03225277664922</v>
       </c>
       <c r="D7" t="n">
-        <v>46.59178254814513</v>
+        <v>33.0574086973986</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>28.53940576245478</v>
+        <v>4.255876297909922</v>
       </c>
       <c r="C8" t="n">
-        <v>144.1156542449105</v>
+        <v>39.63806355896497</v>
       </c>
       <c r="D8" t="n">
-        <v>40.47254910757476</v>
+        <v>35.88287859022092</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14.75468624712531</v>
+        <v>2.995312245657018</v>
       </c>
       <c r="C9" t="n">
-        <v>91.0796797660893</v>
+        <v>25.84843530511426</v>
       </c>
       <c r="D9" t="n">
-        <v>36.72030938194344</v>
+        <v>39.60468413702056</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.687084524252525</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>53.24017800130454</v>
+        <v>26.33538216642069</v>
       </c>
       <c r="D10" t="n">
-        <v>36.72718161587318</v>
+        <v>29.89421759431538</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.153193699591506</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>38.02701557629594</v>
+        <v>22.56743447752142</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>30.91916219754903</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>33.1958351236974</v>
+        <v>18.44213062427633</v>
       </c>
       <c r="D12" t="n">
-        <v>36.23336252063703</v>
+        <v>29.72437524148068</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>30.43908757017236</v>
+        <v>17.69109363052753</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>23.67484588791184</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>19.0517959486136</v>
       </c>
       <c r="D14" t="n">
-        <v>31.65056423721292</v>
+        <v>20.89551813718911</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>24.72531593145592</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>17.91689560250429</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>21.90573652485908</v>
+        <v>22.31905230834699</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>6.611089040398022</v>
       </c>
       <c r="C17" t="n">
-        <v>19.83326712119407</v>
+        <v>44.38874069981529</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>8.02775097762617</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>39.05883241345935</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.028763996121233</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>110.395504946667</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11.0395504946667</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.531567476354029</v>
+        <v>1.153553552490002</v>
       </c>
       <c r="C2" t="n">
-        <v>3.486186097780424</v>
+        <v>5.754023294590556</v>
       </c>
       <c r="D2" t="n">
-        <v>26.40803149653495</v>
+        <v>15.27992126889736</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.91260875878881</v>
+        <v>4.290237467558561</v>
       </c>
       <c r="C3" t="n">
-        <v>35.0582105186536</v>
+        <v>24.83330817892307</v>
       </c>
       <c r="D3" t="n">
-        <v>84.65610453720245</v>
+        <v>77.10155595302325</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.71313404837746</v>
+        <v>17.76570645605028</v>
       </c>
       <c r="C4" t="n">
-        <v>100.6468111439745</v>
+        <v>89.00721036242433</v>
       </c>
       <c r="D4" t="n">
-        <v>106.4793742549048</v>
+        <v>138.0671066390459</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.47130531796326</v>
+        <v>31.1214022246239</v>
       </c>
       <c r="C5" t="n">
-        <v>104.6052178874977</v>
+        <v>190.1154429273949</v>
       </c>
       <c r="D5" t="n">
-        <v>63.96086293167971</v>
+        <v>101.7826932377881</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.82018560586937</v>
+        <v>25.76105975943631</v>
       </c>
       <c r="C6" t="n">
-        <v>117.9776033670435</v>
+        <v>250.3652995370216</v>
       </c>
       <c r="D6" t="n">
-        <v>30.67176177607885</v>
+        <v>52.00513938936205</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.92416874706152</v>
+        <v>9.82140403328509</v>
       </c>
       <c r="C7" t="n">
-        <v>101.3281440507218</v>
+        <v>160.0769084205552</v>
       </c>
       <c r="D7" t="n">
-        <v>28.44613973055133</v>
+        <v>36.53083207502382</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.18072369303942</v>
+        <v>4.589670517353839</v>
       </c>
       <c r="C8" t="n">
-        <v>67.09263810822702</v>
+        <v>66.7588438887831</v>
       </c>
       <c r="D8" t="n">
-        <v>27.03733177495716</v>
+        <v>37.05115835827462</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.435937038414587</v>
+        <v>3.328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>40.60312155223957</v>
+        <v>35.72187196672443</v>
       </c>
       <c r="D9" t="n">
-        <v>27.95624762613216</v>
+        <v>40.38124657107979</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.701188845010476</v>
+        <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>29.75186417719959</v>
+        <v>29.32480392585223</v>
       </c>
       <c r="D10" t="n">
-        <v>28.61303684027329</v>
+        <v>31.74481201682062</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>1.421570675749381</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47675383583222</v>
+        <v>25.9436648324262</v>
       </c>
       <c r="D11" t="n">
-        <v>28.96450251839364</v>
+        <v>31.98534020436108</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>20.82875929330033</v>
       </c>
       <c r="D12" t="n">
-        <v>26.68684784454105</v>
+        <v>30.37527396939631</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>23.67484588791184</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
+        <v>21.20280516861837</v>
+      </c>
+      <c r="D14" t="n">
         <v>20.58823110575986</v>
-      </c>
-      <c r="D14" t="n">
-        <v>23.96838845148163</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.27523351455437</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>22.93362637120549</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>16.94594712300419</v>
+        <v>37.61173629739955</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>12.81278928812512</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.58328130950962</v>
+        <v>46.74984392852887</v>
       </c>
       <c r="D17" t="n">
-        <v>17.47216389248049</v>
+        <v>5.194427103169874</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>73.97468951499715</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.977059949903829</v>
+        <v>0.646971737098648</v>
       </c>
       <c r="C2" t="n">
-        <v>2.178498155723672</v>
+        <v>3.501894061048373</v>
       </c>
       <c r="D2" t="n">
-        <v>18.12993485432585</v>
+        <v>11.8811107167949</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.77163800000477</v>
+        <v>4.201880174176348</v>
       </c>
       <c r="C3" t="n">
-        <v>24.41115666609694</v>
+        <v>23.92028281397354</v>
       </c>
       <c r="D3" t="n">
-        <v>86.22199212547612</v>
+        <v>72.69350876095507</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.65154598491717</v>
+        <v>14.48568737616169</v>
       </c>
       <c r="C4" t="n">
-        <v>97.94111447107029</v>
+        <v>78.92466143980957</v>
       </c>
       <c r="D4" t="n">
-        <v>122.7390797326405</v>
+        <v>144.1804495933908</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.51472320112837</v>
+        <v>31.71045084717198</v>
       </c>
       <c r="C5" t="n">
-        <v>144.145106676038</v>
+        <v>185.9921025695583</v>
       </c>
       <c r="D5" t="n">
-        <v>80.79783605951251</v>
+        <v>121.0740356262379</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.77743067523902</v>
+        <v>30.51075515258238</v>
       </c>
       <c r="C6" t="n">
-        <v>142.5311134502562</v>
+        <v>281.3993262159676</v>
       </c>
       <c r="D6" t="n">
-        <v>38.31957639216151</v>
+        <v>63.91962952810134</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.84620976779852</v>
+        <v>10.30049691295753</v>
       </c>
       <c r="C7" t="n">
-        <v>130.5528097107408</v>
+        <v>229.2459429232642</v>
       </c>
       <c r="D7" t="n">
-        <v>31.02126395879071</v>
+        <v>40.12402867256714</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.511752595819845</v>
+        <v>4.255876297909922</v>
       </c>
       <c r="C8" t="n">
-        <v>88.70581381722054</v>
+        <v>102.892068143587</v>
       </c>
       <c r="D8" t="n">
-        <v>28.28906009787184</v>
+        <v>39.22082078466007</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.548437113775471</v>
+        <v>2.773437264497239</v>
       </c>
       <c r="C9" t="n">
-        <v>46.81562102471339</v>
+        <v>44.81874619427537</v>
       </c>
       <c r="D9" t="n">
-        <v>28.84374755077128</v>
+        <v>40.04843409934012</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>32.31422568528377</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D10" t="n">
-        <v>30.03657101143117</v>
+        <v>33.02599277086271</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>26.65445017030089</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>32.87382187670443</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>21.26269177857742</v>
+        <v>22.56448923440869</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>28.8565102709265</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>16.91060420565131</v>
+        <v>17.43093048890212</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>23.67484588791184</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>16.59349969717959</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>14.33351648200343</v>
+        <v>31.89207417245764</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.75013736150257</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.22610507161303</v>
+        <v>40.09163099832699</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>4.133157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>64.39381366925254</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.75813021185679</v>
+        <v>1.616938468894497</v>
       </c>
       <c r="C2" t="n">
-        <v>5.127668259281091</v>
+        <v>9.141052874242051</v>
       </c>
       <c r="D2" t="n">
-        <v>16.48354395430395</v>
+        <v>15.80024755214817</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.08870145074748</v>
+        <v>3.215223731408304</v>
       </c>
       <c r="C3" t="n">
-        <v>15.77668560724624</v>
+        <v>18.89373456822987</v>
       </c>
       <c r="D3" t="n">
-        <v>81.75504007115313</v>
+        <v>66.2237913899686</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.62449901755476</v>
+        <v>11.52473630015331</v>
       </c>
       <c r="C4" t="n">
-        <v>79.62661104834605</v>
+        <v>69.72274020790422</v>
       </c>
       <c r="D4" t="n">
-        <v>135.5528507684698</v>
+        <v>146.6819427438117</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.20885988575987</v>
+        <v>28.1516154192773</v>
       </c>
       <c r="C5" t="n">
-        <v>161.9392838155114</v>
+        <v>167.3388961888689</v>
       </c>
       <c r="D5" t="n">
-        <v>101.3899941560894</v>
+        <v>139.8745041625643</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.89568236810514</v>
+        <v>35.30070220160257</v>
       </c>
       <c r="C6" t="n">
-        <v>184.8758554298296</v>
+        <v>288.6043726174349</v>
       </c>
       <c r="D6" t="n">
-        <v>52.60891422747383</v>
+        <v>81.14733824222438</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>27.42806736124739</v>
+        <v>19.94224111636546</v>
       </c>
       <c r="C7" t="n">
-        <v>165.5864765367883</v>
+        <v>307.4578555297905</v>
       </c>
       <c r="D7" t="n">
-        <v>34.2551408965797</v>
+        <v>46.71155576806323</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.51728322914683</v>
+        <v>6.592435834017332</v>
       </c>
       <c r="C8" t="n">
-        <v>127.8431860470196</v>
+        <v>183.4199235844316</v>
       </c>
       <c r="D8" t="n">
-        <v>29.87458264023044</v>
+        <v>40.72289477215769</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.879687000734146</v>
+        <v>3.217187226816797</v>
       </c>
       <c r="C9" t="n">
-        <v>74.88280614142545</v>
+        <v>78.09999336824222</v>
       </c>
       <c r="D9" t="n">
-        <v>29.50937249425062</v>
+        <v>40.93593402397924</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.704714925199962</v>
+        <v>1.70824100538945</v>
       </c>
       <c r="C10" t="n">
-        <v>42.13661146627311</v>
+        <v>39.85895679242051</v>
       </c>
       <c r="D10" t="n">
-        <v>30.7483380970101</v>
+        <v>34.44952694202058</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
+        <v>30.74146586308036</v>
+      </c>
+      <c r="D11" t="n">
         <v>33.58460721457913</v>
-      </c>
-      <c r="D11" t="n">
-        <v>30.20837685967435</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>25.60201663134832</v>
+        <v>25.38505038870978</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>29.50740899884213</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>19.77239876353076</v>
       </c>
       <c r="D13" t="n">
-        <v>26.27647730416588</v>
+        <v>24.19517217116264</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>16.59349969717959</v>
+        <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>17.20807376003809</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.5083653843506</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>33.32542582065798</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.46605242207675</v>
+        <v>39.26499943135118</v>
       </c>
       <c r="D16" t="n">
-        <v>14.46605242207675</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>11.33329549782518</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.9050578767911</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.244275251908209</v>
+        <v>1.125082869066845</v>
       </c>
       <c r="C2" t="n">
-        <v>2.363066724122073</v>
+        <v>4.972552122010095</v>
       </c>
       <c r="D2" t="n">
-        <v>11.38630987385451</v>
+        <v>11.50313785065988</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.61255381418778</v>
+        <v>4.898921044191584</v>
       </c>
       <c r="C3" t="n">
-        <v>18.66302385773187</v>
+        <v>27.29749491658256</v>
       </c>
       <c r="D3" t="n">
-        <v>79.86517574047804</v>
+        <v>72.51188543566941</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.61923042613503</v>
+        <v>19.22065655374405</v>
       </c>
       <c r="C4" t="n">
-        <v>73.39840361260428</v>
+        <v>98.59201319898594</v>
       </c>
       <c r="D4" t="n">
-        <v>147.128637949244</v>
+        <v>149.1196222934565</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.34416114249668</v>
+        <v>21.18120671912494</v>
       </c>
       <c r="C5" t="n">
-        <v>183.9795197758523</v>
+        <v>246.9586350032852</v>
       </c>
       <c r="D5" t="n">
-        <v>107.3050240741764</v>
+        <v>125.8109682992288</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.65038431076368</v>
+        <v>12.3572583533546</v>
       </c>
       <c r="C6" t="n">
-        <v>222.3098953927605</v>
+        <v>264.7351406840822</v>
       </c>
       <c r="D6" t="n">
-        <v>51.52211951887262</v>
+        <v>66.97875537453442</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.26435217434965</v>
+        <v>4.311835917051991</v>
       </c>
       <c r="C7" t="n">
-        <v>171.4553643127757</v>
+        <v>128.9957578518054</v>
       </c>
       <c r="D7" t="n">
-        <v>34.37491411649782</v>
+        <v>35.03366682604743</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.005530633326986</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C8" t="n">
-        <v>95.2148010963769</v>
+        <v>57.49605429921444</v>
       </c>
       <c r="D8" t="n">
-        <v>31.54355373745002</v>
+        <v>30.12492830481337</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.220312396378785</v>
       </c>
       <c r="C9" t="n">
-        <v>32.17187226816797</v>
+        <v>30.39687241888974</v>
       </c>
       <c r="D9" t="n">
-        <v>32.06093477758807</v>
+        <v>26.29218526743382</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
+        <v>24.05772749256809</v>
+      </c>
+      <c r="D10" t="n">
         <v>26.33538216642069</v>
-      </c>
-      <c r="D10" t="n">
-        <v>23.63066724122073</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>20.43507846389736</v>
+        <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>23.63361248433346</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.4046032273367</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>19.7439280801076</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>16.65044106402591</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>14.04880964777186</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>8.604036880019047</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.18348900970292</v>
+        <v>33.32542582065798</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>2.866703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9.506263020221864</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.96293993361265</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.821542902005333</v>
+        <v>0.5684319207589033</v>
       </c>
       <c r="C2" t="n">
-        <v>3.114103717870883</v>
+        <v>3.911282853719293</v>
       </c>
       <c r="D2" t="n">
-        <v>15.16407503979623</v>
+        <v>8.977101007632834</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.772537632251</v>
+        <v>4.34914232981337</v>
       </c>
       <c r="C3" t="n">
-        <v>13.77882902910398</v>
+        <v>23.15451960466102</v>
       </c>
       <c r="D3" t="n">
-        <v>71.37796683726434</v>
+        <v>65.37948836431633</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.2881604656256</v>
+        <v>13.51572064436584</v>
       </c>
       <c r="C4" t="n">
-        <v>60.63568345739575</v>
+        <v>79.86910273129502</v>
       </c>
       <c r="D4" t="n">
-        <v>152.5272685748972</v>
+        <v>144.6909583995992</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>51.76264770641309</v>
+        <v>19.65949777754238</v>
       </c>
       <c r="C5" t="n">
-        <v>160.8102739556276</v>
+        <v>195.8586669972387</v>
       </c>
       <c r="D5" t="n">
-        <v>132.045066221196</v>
+        <v>131.7259982173158</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>43.39128503230054</v>
+        <v>11.99499345048753</v>
       </c>
       <c r="C6" t="n">
-        <v>258.8583989264608</v>
+        <v>263.4470876961104</v>
       </c>
       <c r="D6" t="n">
-        <v>67.54227855677206</v>
+        <v>72.57373554103698</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.86428213710246</v>
+        <v>3.653083207502381</v>
       </c>
       <c r="C7" t="n">
-        <v>237.0312022179414</v>
+        <v>169.598879404045</v>
       </c>
       <c r="D7" t="n">
-        <v>39.70482240285375</v>
+        <v>34.37491411649782</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.424156065963627</v>
+        <v>1.084831213192726</v>
       </c>
       <c r="C8" t="n">
-        <v>151.4591270726767</v>
+        <v>66.25815255961723</v>
       </c>
       <c r="D8" t="n">
-        <v>32.96217917008666</v>
+        <v>26.11939767148639</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>63.23436963053704</v>
+        <v>28.17812260729194</v>
       </c>
       <c r="D9" t="n">
-        <v>33.28124717396686</v>
+        <v>20.63437324785945</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>31.60245859970483</v>
+        <v>16.79770321966293</v>
       </c>
       <c r="D10" t="n">
-        <v>24.76949457814703</v>
+        <v>20.07183181332604</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>24.16670148773948</v>
+        <v>12.9718324162131</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>17.23654444346124</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.7912318963607</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="D12" t="n">
-        <v>21.69662426385451</v>
+        <v>13.23494080095125</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>15.86995163914969</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>8.325220532012953</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.82791641431633</v>
+        <v>15.97892563432109</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>3.072870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.25850274585317</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>11.82515109765283</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34.47210713921825</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.997856578142259</v>
+        <v>0.4869468613064179</v>
       </c>
       <c r="C2" t="n">
-        <v>1.987057353395544</v>
+        <v>8.180903619488671</v>
       </c>
       <c r="D2" t="n">
-        <v>10.82573193472958</v>
+        <v>16.4364200645001</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.56989669454866</v>
+        <v>3.082687791334985</v>
       </c>
       <c r="C3" t="n">
-        <v>13.26832022289564</v>
+        <v>18.54030539470102</v>
       </c>
       <c r="D3" t="n">
-        <v>68.02529842726149</v>
+        <v>57.65804267041517</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.88502201207866</v>
+        <v>10.88660029239288</v>
       </c>
       <c r="C4" t="n">
-        <v>50.87220253866122</v>
+        <v>68.39541731176254</v>
       </c>
       <c r="D4" t="n">
-        <v>153.7907778702628</v>
+        <v>144.8951619220825</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>55.54237636776331</v>
+        <v>20.42035224833366</v>
       </c>
       <c r="C5" t="n">
-        <v>145.9613399288945</v>
+        <v>170.2595956090031</v>
       </c>
       <c r="D5" t="n">
-        <v>149.1274762750905</v>
+        <v>153.0299233994716</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>51.4818678629985</v>
+        <v>18.87802660496192</v>
       </c>
       <c r="C6" t="n">
-        <v>271.2559089356895</v>
+        <v>291.5024918403715</v>
       </c>
       <c r="D6" t="n">
-        <v>80.90582830697966</v>
+        <v>94.99390786292139</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.72643654788041</v>
+        <v>8.324238784308704</v>
       </c>
       <c r="C7" t="n">
-        <v>290.9291511810913</v>
+        <v>274.1010137825967</v>
       </c>
       <c r="D7" t="n">
-        <v>44.49575119957818</v>
+        <v>45.51382356888213</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.506221962492859</v>
+        <v>2.253110981246429</v>
       </c>
       <c r="C8" t="n">
-        <v>197.8565235753809</v>
+        <v>143.5315143608837</v>
       </c>
       <c r="D8" t="n">
-        <v>34.88149593188918</v>
+        <v>29.04009709162065</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>0.6656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>74.32811868852599</v>
+        <v>53.58280795008665</v>
       </c>
       <c r="D9" t="n">
-        <v>33.05937219280708</v>
+        <v>22.2984356065578</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>32.74128593663113</v>
+        <v>24.62714116103124</v>
       </c>
       <c r="D10" t="n">
-        <v>25.19655482949439</v>
+        <v>20.78359889890498</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.63361248433346</v>
+        <v>15.81497376771187</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>17.76963344686726</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.57426565372215</v>
+        <v>12.80100831567416</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>13.88583952886689</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>11.44717823151781</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>8.845546815263763</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.06233313145306</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>3.380157345721768</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3481,10 +3481,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.837651775900782</v>
+        <v>0.6970408700152353</v>
       </c>
       <c r="C2" t="n">
-        <v>4.443390109421064</v>
+        <v>15.22985213598077</v>
       </c>
       <c r="D2" t="n">
-        <v>23.08579726536374</v>
+        <v>23.21538796232432</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.24315463548372</v>
+        <v>2.336559536107409</v>
       </c>
       <c r="C3" t="n">
-        <v>10.66178006812036</v>
+        <v>25.58434517267188</v>
       </c>
       <c r="D3" t="n">
-        <v>62.43424525157591</v>
+        <v>57.11808143307943</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.52467954689108</v>
+        <v>8.423395302437632</v>
       </c>
       <c r="C4" t="n">
-        <v>42.72958707963818</v>
+        <v>56.61542660850506</v>
       </c>
       <c r="D4" t="n">
-        <v>150.9574539958066</v>
+        <v>141.3088375584689</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>53.75068680751288</v>
+        <v>18.82501222893259</v>
       </c>
       <c r="C5" t="n">
-        <v>123.0375310347315</v>
+        <v>148.4893402673301</v>
       </c>
       <c r="D5" t="n">
-        <v>165.6944687842554</v>
+        <v>166.1853426363789</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>60.6994970581718</v>
+        <v>22.74218556887737</v>
       </c>
       <c r="C6" t="n">
-        <v>256.3627962622654</v>
+        <v>283.0898957626806</v>
       </c>
       <c r="D6" t="n">
-        <v>101.8366893615217</v>
+        <v>117.6555901200505</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>32.63820242768521</v>
+        <v>14.55244622005047</v>
       </c>
       <c r="C7" t="n">
-        <v>333.807963911775</v>
+        <v>344.3480072645688</v>
       </c>
       <c r="D7" t="n">
-        <v>53.65840252331367</v>
+        <v>58.68887775987432</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.179341034707678</v>
+        <v>5.090361846519712</v>
       </c>
       <c r="C8" t="n">
-        <v>274.9629882669254</v>
+        <v>243.9201258586413</v>
       </c>
       <c r="D8" t="n">
-        <v>37.63529824230147</v>
+        <v>33.79666471869644</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.551562283337459</v>
+        <v>1.331249886958674</v>
       </c>
       <c r="C9" t="n">
-        <v>137.8953007908027</v>
+        <v>108.1640533153923</v>
       </c>
       <c r="D9" t="n">
-        <v>34.05780960802609</v>
+        <v>24.29531043699581</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7117670855789376</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>51.95899724726245</v>
+        <v>41.85190463204153</v>
       </c>
       <c r="D10" t="n">
-        <v>26.76244241776806</v>
+        <v>21.49536598448391</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>28.43141351498762</v>
+        <v>21.32356013624072</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>18.30272245027328</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>20.61179305066178</v>
+        <v>14.97067074205961</v>
       </c>
       <c r="D12" t="n">
-        <v>20.61179305066178</v>
+        <v>14.53673825678252</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>14.56913593102267</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>9.365873098514571</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.67690719431156</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>11.36962016288231</v>
+        <v>3.994731408580272</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>7.525096153051802</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.91561075516378</v>
+        <v>6.839836255487528</v>
       </c>
       <c r="C2" t="n">
-        <v>6.857507714163971</v>
+        <v>10.08942115654447</v>
       </c>
       <c r="D2" t="n">
-        <v>7.555530331883452</v>
+        <v>18.4666743168825</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.712568906833937</v>
+        <v>1.233075116533994</v>
       </c>
       <c r="C2" t="n">
-        <v>2.487748682561417</v>
+        <v>16.44132880302134</v>
       </c>
       <c r="D2" t="n">
-        <v>16.99110751739954</v>
+        <v>22.21596879940107</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.17505419099219</v>
+        <v>2.312015843501239</v>
       </c>
       <c r="C3" t="n">
-        <v>14.33842522052466</v>
+        <v>40.91924431300706</v>
       </c>
       <c r="D3" t="n">
-        <v>71.22579594310609</v>
+        <v>60.53456344385833</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.10046672766521</v>
+        <v>6.496224559001144</v>
       </c>
       <c r="C4" t="n">
-        <v>63.2520410892135</v>
+        <v>59.16797063954677</v>
       </c>
       <c r="D4" t="n">
-        <v>154.6203546803514</v>
+        <v>136.6887328622834</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.17740290149497</v>
+        <v>16.27246819789088</v>
       </c>
       <c r="C5" t="n">
-        <v>202.5100076935109</v>
+        <v>128.6580366415445</v>
       </c>
       <c r="D5" t="n">
-        <v>151.3118649170397</v>
+        <v>176.3218876827272</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>20.24658290468198</v>
+        <v>24.03023855684918</v>
       </c>
       <c r="C6" t="n">
-        <v>272.6244652354096</v>
+        <v>261.8370214611456</v>
       </c>
       <c r="D6" t="n">
-        <v>80.62406671586082</v>
+        <v>135.7688352634042</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.048547605864599</v>
+        <v>19.40326162673396</v>
       </c>
       <c r="C7" t="n">
-        <v>193.37386355779</v>
+        <v>375.0698381735642</v>
       </c>
       <c r="D7" t="n">
-        <v>33.29695513723482</v>
+        <v>74.01984990939251</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.752419652080557</v>
+        <v>9.179341034707678</v>
       </c>
       <c r="C8" t="n">
-        <v>101.6403398206723</v>
+        <v>333.9611165536375</v>
       </c>
       <c r="D8" t="n">
-        <v>25.03456645829366</v>
+        <v>39.22082078466007</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4437499623195582</v>
+        <v>2.773437264497239</v>
       </c>
       <c r="C9" t="n">
-        <v>39.60468413702056</v>
+        <v>185.3765467589954</v>
       </c>
       <c r="D9" t="n">
-        <v>20.41249826669968</v>
+        <v>26.62499773917349</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>22.20713307006285</v>
+        <v>76.01672473983054</v>
       </c>
       <c r="D10" t="n">
-        <v>19.07535789351553</v>
+        <v>22.06477965294707</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>16.52575910558656</v>
+        <v>31.27455486648638</v>
       </c>
       <c r="D11" t="n">
-        <v>16.52575910558656</v>
+        <v>19.01350778814797</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.84831213192725</v>
+        <v>18.44213062427633</v>
       </c>
       <c r="D12" t="n">
-        <v>13.23494080095125</v>
+        <v>15.18763698469816</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.626036240139976</v>
+        <v>15.34962535589888</v>
       </c>
       <c r="D13" t="n">
-        <v>9.365873098514571</v>
+        <v>9.886199381765381</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
         <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>4.609305471438775</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>10.75013736150257</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>0.3583379120500857</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>2.479894700927443</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.142795385472292</v>
+        <v>7.185411447382405</v>
       </c>
       <c r="C2" t="n">
-        <v>4.41982816451914</v>
+        <v>12.92372677870501</v>
       </c>
       <c r="D2" t="n">
-        <v>11.64549126777566</v>
+        <v>22.48005893184347</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.44579557318606</v>
+        <v>11.02011798017045</v>
       </c>
       <c r="C3" t="n">
-        <v>17.27875959474386</v>
+        <v>19.91966091916778</v>
       </c>
       <c r="D3" t="n">
-        <v>9.483682823024187</v>
+        <v>15.56560985083318</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>3.657010198319369</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>8.29576810088555</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>5.675483478250811</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>14.32958949118645</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.19040230136165</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.405903770210439</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.78007281871549</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>46.12250714551515</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.7451308119901</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39868422151458</v>
+        <v>11.67673370913232</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14605268910573</v>
+        <v>59.94056637354591</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576315790766421</v>
+        <v>0.7784489139421547</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.445353604829558</v>
+        <v>3.417463758483147</v>
       </c>
       <c r="C2" t="n">
-        <v>8.579493187412876</v>
+        <v>5.836490101747288</v>
       </c>
       <c r="D2" t="n">
-        <v>28.08092958457152</v>
+        <v>17.621389543526</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.89096925156637</v>
+        <v>19.8362123643068</v>
       </c>
       <c r="C3" t="n">
-        <v>17.26403337918016</v>
+        <v>39.96694903988765</v>
       </c>
       <c r="D3" t="n">
-        <v>16.97441780642735</v>
+        <v>31.43556148998287</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>12.22668590868978</v>
+        <v>13.55400880483146</v>
       </c>
       <c r="C4" t="n">
-        <v>27.28669569183585</v>
+        <v>32.4428346345401</v>
       </c>
       <c r="D4" t="n">
-        <v>20.0374706436774</v>
+        <v>22.53896379409827</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>2.454369260617026</v>
       </c>
       <c r="C5" t="n">
-        <v>5.399612373357458</v>
+        <v>5.129631754689585</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>25.72178985126644</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.366053024963819</v>
+        <v>5.474225198880216</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>13.72581465307466</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>30.06798693796707</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.641744203407924</v>
+        <v>6.767186925373263</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.22360179685679</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>6.842781498600267</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>20.36144738607885</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>25.5156228333746</v>
+        <v>20.85624822901923</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>35.72187196672443</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>6.8329640215578</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>22.91890015564179</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>44.84132639147307</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.463246047684251</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>24.87748682561417</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.57268737340794</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.32528695193774</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44368414724701</v>
+        <v>13.62372412546048</v>
       </c>
       <c r="C21" t="n">
-        <v>86.15950103200962</v>
+        <v>73.72838938484493</v>
       </c>
       <c r="D21" t="n">
-        <v>3.251301925736211</v>
+        <v>1.602791073583586</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.725552611167398</v>
+        <v>2.913827186204533</v>
       </c>
       <c r="C2" t="n">
-        <v>7.899142028369836</v>
+        <v>3.547054455443726</v>
       </c>
       <c r="D2" t="n">
-        <v>23.02591065540469</v>
+        <v>27.26607899004666</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.05157496443535</v>
+        <v>15.2514505854742</v>
       </c>
       <c r="C3" t="n">
-        <v>27.04224051347839</v>
+        <v>29.04991456866312</v>
       </c>
       <c r="D3" t="n">
-        <v>35.49999698556466</v>
+        <v>38.64158963915446</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.73865948868787</v>
+        <v>28.18008610270045</v>
       </c>
       <c r="C4" t="n">
-        <v>36.68005772606933</v>
+        <v>74.30455674362409</v>
       </c>
       <c r="D4" t="n">
-        <v>24.04496477241288</v>
+        <v>33.78292025083699</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>11.1428364432013</v>
+        <v>12.27184630308513</v>
       </c>
       <c r="C5" t="n">
-        <v>31.02322745419922</v>
+        <v>37.99363615435157</v>
       </c>
       <c r="D5" t="n">
-        <v>29.64878066825368</v>
+        <v>28.29887757491431</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.916993413495527</v>
+        <v>4.508185457901354</v>
       </c>
       <c r="C6" t="n">
-        <v>12.11574841810989</v>
+        <v>10.58618549489336</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>31.55729820530948</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>6.94684675525043</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.82246789644735</v>
       </c>
       <c r="D7" t="n">
-        <v>37.42913122440964</v>
+        <v>32.81786225756237</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.51451791248334</v>
+        <v>7.42692138262712</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>23.699389580518</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>34.29735604786232</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>29.62030998483051</v>
+        <v>23.96249796525614</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>36.27655941962388</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.537678946757763</v>
+        <v>7.260024272905163</v>
       </c>
       <c r="C10" t="n">
-        <v>29.46715734296802</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.4142661401257</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.174031385558941</v>
+        <v>6.397068040872215</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>44.77947628610551</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>41.44055234396211</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>44.48789721794422</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.65583282863265</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>43.35888735806038</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73793981377011</v>
+        <v>14.82783519676882</v>
       </c>
       <c r="C21" t="n">
-        <v>102.1014328639977</v>
+        <v>87.31947393652753</v>
       </c>
       <c r="D21" t="n">
-        <v>5.021381944131034</v>
+        <v>2.471305866128137</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.014186436215961</v>
+        <v>1.904590546238812</v>
       </c>
       <c r="C2" t="n">
-        <v>5.477170441992955</v>
+        <v>8.098436812331938</v>
       </c>
       <c r="D2" t="n">
-        <v>26.34225440035042</v>
+        <v>25.60398012675682</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.01016163440774</v>
+        <v>12.46328710541326</v>
       </c>
       <c r="C3" t="n">
-        <v>29.11372816943916</v>
+        <v>19.93929587325272</v>
       </c>
       <c r="D3" t="n">
-        <v>45.10148953309847</v>
+        <v>51.48775834922397</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.83549265850982</v>
+        <v>28.93308659185775</v>
       </c>
       <c r="C4" t="n">
-        <v>53.9863062565321</v>
+        <v>73.43669177306991</v>
       </c>
       <c r="D4" t="n">
-        <v>35.76114187489431</v>
+        <v>45.55014823393926</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>23.26742059064941</v>
+        <v>27.93072218582176</v>
       </c>
       <c r="C5" t="n">
-        <v>50.56000676871075</v>
+        <v>93.5850999073272</v>
       </c>
       <c r="D5" t="n">
-        <v>31.31775176547326</v>
+        <v>34.11573272257667</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.58618549489336</v>
+        <v>10.6666888066416</v>
       </c>
       <c r="C6" t="n">
-        <v>31.67805317293184</v>
+        <v>37.15227837181205</v>
       </c>
       <c r="D6" t="n">
-        <v>38.15856976866503</v>
+        <v>33.36862271964485</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.563785224144926</v>
+        <v>6.407867265618931</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19985992550562</v>
+        <v>17.66654993792135</v>
       </c>
       <c r="D7" t="n">
-        <v>39.46527596301753</v>
+        <v>34.97378021608837</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.93176068678823</v>
+        <v>7.844164156932015</v>
       </c>
       <c r="C8" t="n">
-        <v>31.54355373745002</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>35.79943003535994</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>7.765624340592267</v>
       </c>
       <c r="C9" t="n">
-        <v>34.27968458918587</v>
+        <v>27.5124976638126</v>
       </c>
       <c r="D9" t="n">
-        <v>41.93437143919824</v>
+        <v>36.94218436310322</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>7.544731107136738</v>
       </c>
       <c r="C10" t="n">
-        <v>33.16834618797849</v>
+        <v>27.47420950334699</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.27191272300992</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>6.930157044278233</v>
       </c>
       <c r="C11" t="n">
-        <v>33.40691088011046</v>
+        <v>28.25371718051895</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>45.31256528951153</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.159886007071988</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>34.71459882216721</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>42.95931604243193</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>28.09761929554372</v>
       </c>
       <c r="D13" t="n">
-        <v>45.52854978444583</v>
+        <v>41.62610266006477</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.42141611149592</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>29.02537087605695</v>
+        <v>25.44199175555609</v>
       </c>
       <c r="D15" t="n">
-        <v>44.07556318216055</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.06479365701439</v>
+        <v>16.05937165871375</v>
       </c>
       <c r="C21" t="n">
-        <v>117.8512729052844</v>
+        <v>100.5823803887861</v>
       </c>
       <c r="D21" t="n">
-        <v>6.881826155053102</v>
+        <v>3.380920349202896</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.8791061636574</v>
+        <v>1.670934592628071</v>
       </c>
       <c r="C2" t="n">
-        <v>10.83947640258903</v>
+        <v>10.68926900383927</v>
       </c>
       <c r="D2" t="n">
-        <v>29.37781830188155</v>
+        <v>33.34604252244716</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.3278469799562</v>
+        <v>9.238245896962486</v>
       </c>
       <c r="C3" t="n">
-        <v>23.12506717353362</v>
+        <v>26.42864819832414</v>
       </c>
       <c r="D3" t="n">
-        <v>51.82646130718912</v>
+        <v>59.49391087735671</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.98565899953057</v>
+        <v>26.49540704221292</v>
       </c>
       <c r="C4" t="n">
-        <v>54.02459441699773</v>
+        <v>60.49529353568845</v>
       </c>
       <c r="D4" t="n">
-        <v>43.24009588584652</v>
+        <v>60.2655645728947</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>20.10128424445345</v>
+        <v>35.80924751240241</v>
       </c>
       <c r="C5" t="n">
-        <v>56.79410469067799</v>
+        <v>115.8707727937298</v>
       </c>
       <c r="D5" t="n">
-        <v>29.57514959043517</v>
+        <v>42.31332605303754</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.43147026824986</v>
+        <v>23.58747034223387</v>
       </c>
       <c r="C6" t="n">
-        <v>38.7220929509027</v>
+        <v>93.70585487494957</v>
       </c>
       <c r="D6" t="n">
-        <v>30.75226508782709</v>
+        <v>36.26674194258143</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.329908286355933</v>
+        <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>21.4992929753009</v>
+        <v>35.51275970571987</v>
       </c>
       <c r="D7" t="n">
-        <v>30.72183090899544</v>
+        <v>37.00992495469625</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>7.677267047210056</v>
       </c>
       <c r="C8" t="n">
-        <v>18.60902773399829</v>
+        <v>25.11801501315464</v>
       </c>
       <c r="D8" t="n">
-        <v>30.37527396939631</v>
+        <v>37.05115835827462</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>8.209374302911826</v>
       </c>
       <c r="C9" t="n">
-        <v>21.85468564423824</v>
+        <v>30.39687241888974</v>
       </c>
       <c r="D9" t="n">
-        <v>29.95312245657017</v>
+        <v>38.162496759482</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.412955930589413</v>
+        <v>7.829437941368314</v>
       </c>
       <c r="C10" t="n">
-        <v>21.49536598448391</v>
+        <v>30.7483380970101</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>44.27191272300992</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>7.285549713215578</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>30.38607319414302</v>
       </c>
       <c r="D11" t="n">
-        <v>34.47308888692249</v>
+        <v>45.66795795844887</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>31.24313893995049</v>
       </c>
       <c r="D12" t="n">
-        <v>32.11100391050467</v>
+        <v>44.04414725562465</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>30.69925071179776</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>42.40659208494097</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>28.5776939229204</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>27.27884171020187</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.605157496443535</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.060483038199038</v>
+        <v>17.31302478272607</v>
       </c>
       <c r="C21" t="n">
-        <v>66.19202848311598</v>
+        <v>113.4003123268558</v>
       </c>
       <c r="D21" t="n">
-        <v>5.295362278649279</v>
+        <v>4.328256195681517</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.814490741626358</v>
+        <v>2.267837196810132</v>
       </c>
       <c r="C2" t="n">
-        <v>6.021058670145687</v>
+        <v>10.06585921164255</v>
       </c>
       <c r="D2" t="n">
-        <v>21.86155787816798</v>
+        <v>43.18119102359171</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.51990967709008</v>
+        <v>7.436738859669589</v>
       </c>
       <c r="C3" t="n">
-        <v>35.52944941669207</v>
+        <v>34.23354244708628</v>
       </c>
       <c r="D3" t="n">
-        <v>63.98049788576463</v>
+        <v>70.07715112913733</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.92857876396402</v>
+        <v>21.91359050649305</v>
       </c>
       <c r="C4" t="n">
-        <v>56.58990116819465</v>
+        <v>63.2520410892135</v>
       </c>
       <c r="D4" t="n">
-        <v>59.94649656901449</v>
+        <v>73.258013690897</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.66703296400687</v>
+        <v>37.65002445786519</v>
       </c>
       <c r="C5" t="n">
-        <v>83.17857424231102</v>
+        <v>112.5573742918968</v>
       </c>
       <c r="D5" t="n">
-        <v>39.46625771072178</v>
+        <v>53.01437602932777</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>20.40758952817845</v>
+        <v>35.17994723398021</v>
       </c>
       <c r="C6" t="n">
-        <v>68.66932492124741</v>
+        <v>137.1373915631242</v>
       </c>
       <c r="D6" t="n">
-        <v>33.6906359666378</v>
+        <v>40.49316580936395</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.18072369303942</v>
+        <v>17.84620976779852</v>
       </c>
       <c r="C7" t="n">
-        <v>41.98051358129786</v>
+        <v>82.28420208374216</v>
       </c>
       <c r="D7" t="n">
-        <v>32.87774886752143</v>
+        <v>39.28561613314036</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.591053175685585</v>
+        <v>9.095892479846697</v>
       </c>
       <c r="C8" t="n">
-        <v>24.78422079371073</v>
+        <v>35.29873870619407</v>
       </c>
       <c r="D8" t="n">
-        <v>32.3780392860598</v>
+        <v>38.80357801035517</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>8.209374302911826</v>
       </c>
       <c r="C9" t="n">
-        <v>23.2968730217768</v>
+        <v>31.61718481526852</v>
       </c>
       <c r="D9" t="n">
-        <v>31.17343485294896</v>
+        <v>38.82812170296133</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.840016181936776</v>
+        <v>8.114144775599888</v>
       </c>
       <c r="C10" t="n">
-        <v>24.76949457814703</v>
+        <v>34.02246669067321</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>44.4142661401257</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>33.05151821117311</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>45.84565429291754</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>6.508987279156352</v>
       </c>
       <c r="C12" t="n">
-        <v>22.1305567491316</v>
+        <v>33.1958351236974</v>
       </c>
       <c r="D12" t="n">
-        <v>32.97886888105885</v>
+        <v>44.91201222617883</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>21.33337761328319</v>
+        <v>33.04071898642641</v>
       </c>
       <c r="D13" t="n">
-        <v>31.21957699504857</v>
+        <v>42.66675522656638</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.35908298004286</v>
+        <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>41.20885988575986</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>24.07245370813179</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>35.64235040268044</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>16.13993225781756</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.282365504383439</v>
+        <v>17.69596671637213</v>
       </c>
       <c r="C21" t="n">
-        <v>75.55454210797819</v>
+        <v>126.5261620220607</v>
       </c>
       <c r="D21" t="n">
-        <v>6.372069816335509</v>
+        <v>5.308790014911637</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.783655652167207</v>
+        <v>2.080323385298991</v>
       </c>
       <c r="C2" t="n">
-        <v>8.383143646563514</v>
+        <v>6.360743375815084</v>
       </c>
       <c r="D2" t="n">
-        <v>21.67011707583984</v>
+        <v>34.2571043919882</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.78574232076272</v>
+        <v>12.18348900970292</v>
       </c>
       <c r="C3" t="n">
-        <v>28.19088532744716</v>
+        <v>49.95623193059895</v>
       </c>
       <c r="D3" t="n">
-        <v>66.62139921018856</v>
+        <v>76.82175785731292</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.87149852839745</v>
+        <v>18.08477445993049</v>
       </c>
       <c r="C4" t="n">
-        <v>75.6701678002314</v>
+        <v>94.43136642838796</v>
       </c>
       <c r="D4" t="n">
-        <v>78.54177983515332</v>
+        <v>67.74451858384691</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.33095645398497</v>
+        <v>19.8067599331794</v>
       </c>
       <c r="C5" t="n">
-        <v>95.47496423800231</v>
+        <v>81.92684591939634</v>
       </c>
       <c r="D5" t="n">
-        <v>51.71356032120075</v>
+        <v>39.44171401811561</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.51075515258238</v>
+        <v>11.06920536538279</v>
       </c>
       <c r="C6" t="n">
-        <v>102.963735725997</v>
+        <v>54.17872880656449</v>
       </c>
       <c r="D6" t="n">
-        <v>38.84284791852506</v>
+        <v>25.84156307118455</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.66654993792135</v>
+        <v>5.988660995905543</v>
       </c>
       <c r="C7" t="n">
-        <v>73.78030346955629</v>
+        <v>24.79305652304895</v>
       </c>
       <c r="D7" t="n">
-        <v>35.2133266559246</v>
+        <v>27.24840753137022</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.678649705541805</v>
+        <v>5.674501730546564</v>
       </c>
       <c r="C8" t="n">
-        <v>41.8911745402114</v>
+        <v>23.28214680621311</v>
       </c>
       <c r="D8" t="n">
-        <v>34.38080460272329</v>
+        <v>28.62285431731576</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.546874528994477</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>27.95624762613216</v>
+        <v>25.95937279569415</v>
       </c>
       <c r="D9" t="n">
-        <v>32.72655972106742</v>
+        <v>33.83593462686631</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>26.90479583488384</v>
+        <v>25.90832191507333</v>
       </c>
       <c r="D10" t="n">
-        <v>34.30717352490479</v>
+        <v>35.87306111317846</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>26.83214650476957</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>35.89465956267188</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>24.95111790343269</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>34.06370009425158</v>
+        <v>34.71459882216721</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.41468274628643</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>31.47974013667398</v>
+        <v>34.60169783617884</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>21.51009220004762</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>34.41614752007619</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>32.25041208450772</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>24.79894700927443</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>30.17205219461722</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>25.97213551584937</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>30.69237847786803</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>13.84166088217578</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>13.4499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>96.16709636949629</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.491539869930473</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>85.21626602045913</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.491539869930473</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
